--- a/src/test/resources/TestDriver/Hearst_Ver/ActivityData/VER_PSD_2025-05-31.xlsx
+++ b/src/test/resources/TestDriver/Hearst_Ver/ActivityData/VER_PSD_2025-05-31.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\fyntrac-data\src\test\resources\TestDriver\Hearst_Ver\ActivityData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A98392-0EE6-4545-9399-279D925B6F23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65F1E464-5D78-4610-BFDF-E14D0507C6F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3975" yWindow="3975" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PSDLogs" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -682,9 +695,6 @@
     <t>6oqLiUfW4MPT2K7i-16693</t>
   </si>
   <si>
-    <t>hJAJPF_hfI63</t>
-  </si>
-  <si>
     <t>VER_515_249387721_2507400074117</t>
   </si>
   <si>
@@ -1132,9 +1142,6 @@
     <t>16BjmtUfVskrC22UT-16687</t>
   </si>
   <si>
-    <t>AUWkm4lmix6I</t>
-  </si>
-  <si>
     <t>VER_515_105862471_2507400065613</t>
   </si>
   <si>
@@ -1870,9 +1877,6 @@
     <t>AzZuGjUfXYeQT4kNn-16756</t>
   </si>
   <si>
-    <t>0fAS30hM7l2P</t>
-  </si>
-  <si>
     <t>VER_515_249387941_2507400135120</t>
   </si>
   <si>
@@ -2041,9 +2045,6 @@
     <t>AzyVkrUfYP9ca64Qb-16784</t>
   </si>
   <si>
-    <t>tA6b8Wq2bQib</t>
-  </si>
-  <si>
     <t>VER_515_65279740_2507500151727</t>
   </si>
   <si>
@@ -2221,9 +2222,6 @@
     <t>AzqS6AUfXMYaz4TiL-16748</t>
   </si>
   <si>
-    <t>HVsBa9u3-XRl</t>
-  </si>
-  <si>
     <t>VER_515_249387915_2507402130152</t>
   </si>
   <si>
@@ -2864,6 +2862,21 @@
   </si>
   <si>
     <t>VER_515_249442582_2508300155617</t>
+  </si>
+  <si>
+    <t>ks0zSbX_hf</t>
+  </si>
+  <si>
+    <t>SxrZV_erYJ</t>
+  </si>
+  <si>
+    <t>5VrGPHcv_c</t>
+  </si>
+  <si>
+    <t>EgzP7nc5d7m</t>
+  </si>
+  <si>
+    <t>EMCTbgEcLB</t>
   </si>
 </sst>
 </file>
@@ -2871,9 +2884,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yy"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2896,6 +2909,18 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2914,17 +2939,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{CD4629AF-6366-4A31-A2CC-0C6288FE25D6}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -3269,10 +3297,10 @@
       <c r="B2" s="3">
         <v>45762</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E2" t="s">
@@ -3298,10 +3326,10 @@
       <c r="B3" s="3">
         <v>45762</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E3" t="s">
@@ -3327,10 +3355,10 @@
       <c r="B4" s="3">
         <v>45762</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E4" t="s">
@@ -3356,10 +3384,10 @@
       <c r="B5" s="3">
         <v>45762</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="4" t="s">
         <v>22</v>
       </c>
       <c r="E5" t="s">
@@ -3385,10 +3413,10 @@
       <c r="B6" s="3">
         <v>45762</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="4" t="s">
         <v>25</v>
       </c>
       <c r="E6" t="s">
@@ -3414,10 +3442,10 @@
       <c r="B7" s="3">
         <v>45762</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="4" t="s">
         <v>28</v>
       </c>
       <c r="E7" t="s">
@@ -3443,10 +3471,10 @@
       <c r="B8" s="3">
         <v>45762</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E8" t="s">
@@ -3472,10 +3500,10 @@
       <c r="B9" s="3">
         <v>45762</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E9" t="s">
@@ -3501,10 +3529,10 @@
       <c r="B10" s="3">
         <v>45762</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="4" t="s">
         <v>37</v>
       </c>
       <c r="E10" t="s">
@@ -3530,10 +3558,10 @@
       <c r="B11" s="3">
         <v>45762</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="4" t="s">
         <v>40</v>
       </c>
       <c r="E11" t="s">
@@ -3559,10 +3587,10 @@
       <c r="B12" s="3">
         <v>45762</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="4" t="s">
         <v>43</v>
       </c>
       <c r="E12" t="s">
@@ -3588,10 +3616,10 @@
       <c r="B13" s="3">
         <v>45762</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="4" t="s">
         <v>46</v>
       </c>
       <c r="E13" t="s">
@@ -3617,10 +3645,10 @@
       <c r="B14" s="3">
         <v>45762</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="4" t="s">
         <v>49</v>
       </c>
       <c r="E14" t="s">
@@ -3646,10 +3674,10 @@
       <c r="B15" s="3">
         <v>45762</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="4" t="s">
         <v>52</v>
       </c>
       <c r="E15" t="s">
@@ -3675,10 +3703,10 @@
       <c r="B16" s="3">
         <v>45762</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="4" t="s">
         <v>55</v>
       </c>
       <c r="E16" t="s">
@@ -3704,10 +3732,10 @@
       <c r="B17" s="3">
         <v>45762</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="4" t="s">
         <v>58</v>
       </c>
       <c r="E17" t="s">
@@ -3733,10 +3761,10 @@
       <c r="B18" s="3">
         <v>45762</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="4" t="s">
         <v>61</v>
       </c>
       <c r="E18" t="s">
@@ -3762,10 +3790,10 @@
       <c r="B19" s="3">
         <v>45762</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="4" t="s">
         <v>64</v>
       </c>
       <c r="E19" t="s">
@@ -3791,10 +3819,10 @@
       <c r="B20" s="3">
         <v>45762</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="4" t="s">
         <v>67</v>
       </c>
       <c r="E20" t="s">
@@ -3820,10 +3848,10 @@
       <c r="B21" s="3">
         <v>45762</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="4" t="s">
         <v>70</v>
       </c>
       <c r="E21" t="s">
@@ -3849,10 +3877,10 @@
       <c r="B22" s="3">
         <v>45762</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="4" t="s">
         <v>73</v>
       </c>
       <c r="E22" t="s">
@@ -3878,10 +3906,10 @@
       <c r="B23" s="3">
         <v>45762</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="4" t="s">
         <v>76</v>
       </c>
       <c r="E23" t="s">
@@ -3907,10 +3935,10 @@
       <c r="B24" s="3">
         <v>45762</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="4" t="s">
         <v>79</v>
       </c>
       <c r="E24" t="s">
@@ -3936,10 +3964,10 @@
       <c r="B25" s="3">
         <v>45762</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="4" t="s">
         <v>82</v>
       </c>
       <c r="E25" t="s">
@@ -3965,10 +3993,10 @@
       <c r="B26" s="3">
         <v>45762</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="4" t="s">
         <v>85</v>
       </c>
       <c r="E26" t="s">
@@ -3994,10 +4022,10 @@
       <c r="B27" s="3">
         <v>45762</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="4" t="s">
         <v>88</v>
       </c>
       <c r="E27" t="s">
@@ -4023,10 +4051,10 @@
       <c r="B28" s="3">
         <v>45762</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="4" t="s">
         <v>91</v>
       </c>
       <c r="E28" t="s">
@@ -4052,10 +4080,10 @@
       <c r="B29" s="3">
         <v>45762</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="4" t="s">
         <v>94</v>
       </c>
       <c r="E29" t="s">
@@ -4081,10 +4109,10 @@
       <c r="B30" s="3">
         <v>45762</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="4" t="s">
         <v>97</v>
       </c>
       <c r="E30" t="s">
@@ -4110,10 +4138,10 @@
       <c r="B31" s="3">
         <v>45762</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="4" t="s">
         <v>100</v>
       </c>
       <c r="E31" t="s">
@@ -4139,10 +4167,10 @@
       <c r="B32" s="3">
         <v>45762</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="4" t="s">
         <v>103</v>
       </c>
       <c r="E32" t="s">
@@ -4168,10 +4196,10 @@
       <c r="B33" s="3">
         <v>45762</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="4" t="s">
         <v>106</v>
       </c>
       <c r="E33" t="s">
@@ -4197,10 +4225,10 @@
       <c r="B34" s="3">
         <v>45762</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="4" t="s">
         <v>109</v>
       </c>
       <c r="E34" t="s">
@@ -4226,10 +4254,10 @@
       <c r="B35" s="3">
         <v>45762</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="4" t="s">
         <v>112</v>
       </c>
       <c r="E35" t="s">
@@ -4255,10 +4283,10 @@
       <c r="B36" s="3">
         <v>45762</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" s="4" t="s">
         <v>115</v>
       </c>
       <c r="E36" t="s">
@@ -4284,10 +4312,10 @@
       <c r="B37" s="3">
         <v>45762</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" s="4" t="s">
         <v>118</v>
       </c>
       <c r="E37" t="s">
@@ -4313,10 +4341,10 @@
       <c r="B38" s="3">
         <v>45762</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" s="4" t="s">
         <v>121</v>
       </c>
       <c r="E38" t="s">
@@ -4342,10 +4370,10 @@
       <c r="B39" s="3">
         <v>45762</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="4" t="s">
         <v>124</v>
       </c>
       <c r="E39" t="s">
@@ -4371,10 +4399,10 @@
       <c r="B40" s="3">
         <v>45762</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D40" s="4" t="s">
         <v>127</v>
       </c>
       <c r="E40" t="s">
@@ -4400,10 +4428,10 @@
       <c r="B41" s="3">
         <v>45762</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D41" s="4" t="s">
         <v>130</v>
       </c>
       <c r="E41" t="s">
@@ -4429,10 +4457,10 @@
       <c r="B42" s="3">
         <v>45762</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" s="4" t="s">
         <v>133</v>
       </c>
       <c r="E42" t="s">
@@ -4458,10 +4486,10 @@
       <c r="B43" s="3">
         <v>45762</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D43" s="4" t="s">
         <v>136</v>
       </c>
       <c r="E43" t="s">
@@ -4487,10 +4515,10 @@
       <c r="B44" s="3">
         <v>45762</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D44" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E44" t="s">
@@ -4516,10 +4544,10 @@
       <c r="B45" s="3">
         <v>45762</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D45" s="4" t="s">
         <v>142</v>
       </c>
       <c r="E45" t="s">
@@ -4545,10 +4573,10 @@
       <c r="B46" s="3">
         <v>45762</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D46" s="4" t="s">
         <v>145</v>
       </c>
       <c r="E46" t="s">
@@ -4574,10 +4602,10 @@
       <c r="B47" s="3">
         <v>45762</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D47" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E47" t="s">
@@ -4603,10 +4631,10 @@
       <c r="B48" s="3">
         <v>45762</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D48" s="4" t="s">
         <v>151</v>
       </c>
       <c r="E48" t="s">
@@ -4632,10 +4660,10 @@
       <c r="B49" s="3">
         <v>45762</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D49" s="4" t="s">
         <v>154</v>
       </c>
       <c r="E49" t="s">
@@ -4661,10 +4689,10 @@
       <c r="B50" s="3">
         <v>45762</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D50" s="4" t="s">
         <v>157</v>
       </c>
       <c r="E50" t="s">
@@ -4690,10 +4718,10 @@
       <c r="B51" s="3">
         <v>45762</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D51" s="4" t="s">
         <v>160</v>
       </c>
       <c r="E51" t="s">
@@ -4719,10 +4747,10 @@
       <c r="B52" s="3">
         <v>45762</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D52" s="4" t="s">
         <v>163</v>
       </c>
       <c r="E52" t="s">
@@ -4748,10 +4776,10 @@
       <c r="B53" s="3">
         <v>45762</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D53" s="4" t="s">
         <v>166</v>
       </c>
       <c r="E53" t="s">
@@ -4777,10 +4805,10 @@
       <c r="B54" s="3">
         <v>45762</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C54" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D54" s="4" t="s">
         <v>169</v>
       </c>
       <c r="E54" t="s">
@@ -4806,10 +4834,10 @@
       <c r="B55" s="3">
         <v>45762</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="D55" t="s">
+      <c r="D55" s="4" t="s">
         <v>172</v>
       </c>
       <c r="E55" t="s">
@@ -4835,10 +4863,10 @@
       <c r="B56" s="3">
         <v>45762</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C56" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D56" s="4" t="s">
         <v>175</v>
       </c>
       <c r="E56" t="s">
@@ -4864,10 +4892,10 @@
       <c r="B57" s="3">
         <v>45762</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C57" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="D57" t="s">
+      <c r="D57" s="4" t="s">
         <v>178</v>
       </c>
       <c r="E57" t="s">
@@ -4893,10 +4921,10 @@
       <c r="B58" s="3">
         <v>45762</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D58" s="4" t="s">
         <v>181</v>
       </c>
       <c r="E58" t="s">
@@ -4922,10 +4950,10 @@
       <c r="B59" s="3">
         <v>45762</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C59" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="D59" t="s">
+      <c r="D59" s="4" t="s">
         <v>184</v>
       </c>
       <c r="E59" t="s">
@@ -4951,10 +4979,10 @@
       <c r="B60" s="3">
         <v>45762</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D60" s="4" t="s">
         <v>187</v>
       </c>
       <c r="E60" t="s">
@@ -4980,10 +5008,10 @@
       <c r="B61" s="3">
         <v>45762</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="D61" t="s">
+      <c r="D61" s="4" t="s">
         <v>190</v>
       </c>
       <c r="E61" t="s">
@@ -5009,10 +5037,10 @@
       <c r="B62" s="3">
         <v>45762</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D62" s="4" t="s">
         <v>193</v>
       </c>
       <c r="E62" t="s">
@@ -5038,10 +5066,10 @@
       <c r="B63" s="3">
         <v>45762</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C63" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D63" s="4" t="s">
         <v>196</v>
       </c>
       <c r="E63" t="s">
@@ -5067,10 +5095,10 @@
       <c r="B64" s="3">
         <v>45762</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C64" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D64" s="4" t="s">
         <v>199</v>
       </c>
       <c r="E64" t="s">
@@ -5096,10 +5124,10 @@
       <c r="B65" s="3">
         <v>45762</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C65" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D65" s="4" t="s">
         <v>202</v>
       </c>
       <c r="E65" t="s">
@@ -5125,10 +5153,10 @@
       <c r="B66" s="3">
         <v>45762</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C66" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="D66" t="s">
+      <c r="D66" s="4" t="s">
         <v>205</v>
       </c>
       <c r="E66" t="s">
@@ -5154,10 +5182,10 @@
       <c r="B67" s="3">
         <v>45762</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C67" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="D67" t="s">
+      <c r="D67" s="4" t="s">
         <v>208</v>
       </c>
       <c r="E67" t="s">
@@ -5183,10 +5211,10 @@
       <c r="B68" s="3">
         <v>45762</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C68" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="D68" t="s">
+      <c r="D68" s="4" t="s">
         <v>211</v>
       </c>
       <c r="E68" t="s">
@@ -5212,10 +5240,10 @@
       <c r="B69" s="3">
         <v>45762</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C69" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="D69" t="s">
+      <c r="D69" s="4" t="s">
         <v>214</v>
       </c>
       <c r="E69" t="s">
@@ -5241,10 +5269,10 @@
       <c r="B70" s="3">
         <v>45762</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C70" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="D70" t="s">
+      <c r="D70" s="4" t="s">
         <v>217</v>
       </c>
       <c r="E70" t="s">
@@ -5270,11 +5298,11 @@
       <c r="B71" s="3">
         <v>45762</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C71" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="D71" t="s">
-        <v>220</v>
+      <c r="D71" s="4" t="s">
+        <v>943</v>
       </c>
       <c r="E71" t="s">
         <v>11</v>
@@ -5283,7 +5311,7 @@
         <v>12</v>
       </c>
       <c r="G71" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H71">
         <v>0.16669999999999999</v>
@@ -5299,11 +5327,11 @@
       <c r="B72" s="3">
         <v>45762</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C72" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="D72" s="4" t="s">
         <v>222</v>
-      </c>
-      <c r="D72" t="s">
-        <v>223</v>
       </c>
       <c r="E72" t="s">
         <v>11</v>
@@ -5312,7 +5340,7 @@
         <v>12</v>
       </c>
       <c r="G72" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H72">
         <v>0.16669999999999999</v>
@@ -5328,20 +5356,20 @@
       <c r="B73" s="3">
         <v>45762</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C73" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="D73" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="D73" t="s">
+      <c r="E73" t="s">
+        <v>11</v>
+      </c>
+      <c r="F73" t="s">
+        <v>16</v>
+      </c>
+      <c r="G73" t="s">
         <v>226</v>
-      </c>
-      <c r="E73" t="s">
-        <v>11</v>
-      </c>
-      <c r="F73" t="s">
-        <v>16</v>
-      </c>
-      <c r="G73" t="s">
-        <v>227</v>
       </c>
       <c r="H73">
         <v>0.16669999999999999</v>
@@ -5357,11 +5385,11 @@
       <c r="B74" s="3">
         <v>45762</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C74" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="D74" s="4" t="s">
         <v>228</v>
-      </c>
-      <c r="D74" t="s">
-        <v>229</v>
       </c>
       <c r="E74" t="s">
         <v>11</v>
@@ -5370,7 +5398,7 @@
         <v>12</v>
       </c>
       <c r="G74" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H74">
         <v>0.16669999999999999</v>
@@ -5386,20 +5414,20 @@
       <c r="B75" s="3">
         <v>45762</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C75" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="D75" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="D75" t="s">
+      <c r="E75" t="s">
+        <v>11</v>
+      </c>
+      <c r="F75" t="s">
+        <v>16</v>
+      </c>
+      <c r="G75" t="s">
         <v>232</v>
-      </c>
-      <c r="E75" t="s">
-        <v>11</v>
-      </c>
-      <c r="F75" t="s">
-        <v>16</v>
-      </c>
-      <c r="G75" t="s">
-        <v>233</v>
       </c>
       <c r="H75">
         <v>0.16669999999999999</v>
@@ -5415,11 +5443,11 @@
       <c r="B76" s="3">
         <v>45762</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C76" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="D76" s="4" t="s">
         <v>234</v>
-      </c>
-      <c r="D76" t="s">
-        <v>235</v>
       </c>
       <c r="E76" t="s">
         <v>11</v>
@@ -5428,7 +5456,7 @@
         <v>12</v>
       </c>
       <c r="G76" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H76">
         <v>0.16669999999999999</v>
@@ -5444,20 +5472,20 @@
       <c r="B77" s="3">
         <v>45762</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C77" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="D77" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="D77" t="s">
+      <c r="E77" t="s">
+        <v>11</v>
+      </c>
+      <c r="F77" t="s">
+        <v>16</v>
+      </c>
+      <c r="G77" t="s">
         <v>238</v>
-      </c>
-      <c r="E77" t="s">
-        <v>11</v>
-      </c>
-      <c r="F77" t="s">
-        <v>16</v>
-      </c>
-      <c r="G77" t="s">
-        <v>239</v>
       </c>
       <c r="H77">
         <v>0.16669999999999999</v>
@@ -5473,20 +5501,20 @@
       <c r="B78" s="3">
         <v>45762</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C78" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="D78" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="D78" t="s">
+      <c r="E78" t="s">
+        <v>11</v>
+      </c>
+      <c r="F78" t="s">
+        <v>16</v>
+      </c>
+      <c r="G78" t="s">
         <v>241</v>
-      </c>
-      <c r="E78" t="s">
-        <v>11</v>
-      </c>
-      <c r="F78" t="s">
-        <v>16</v>
-      </c>
-      <c r="G78" t="s">
-        <v>242</v>
       </c>
       <c r="H78">
         <v>0.16669999999999999</v>
@@ -5502,11 +5530,11 @@
       <c r="B79" s="3">
         <v>45762</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C79" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D79" s="4" t="s">
         <v>243</v>
-      </c>
-      <c r="D79" t="s">
-        <v>244</v>
       </c>
       <c r="E79" t="s">
         <v>11</v>
@@ -5515,7 +5543,7 @@
         <v>12</v>
       </c>
       <c r="G79" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H79">
         <v>0.16669999999999999</v>
@@ -5531,20 +5559,20 @@
       <c r="B80" s="3">
         <v>45762</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C80" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="D80" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="D80" t="s">
+      <c r="E80" t="s">
+        <v>11</v>
+      </c>
+      <c r="F80" t="s">
+        <v>16</v>
+      </c>
+      <c r="G80" t="s">
         <v>247</v>
-      </c>
-      <c r="E80" t="s">
-        <v>11</v>
-      </c>
-      <c r="F80" t="s">
-        <v>16</v>
-      </c>
-      <c r="G80" t="s">
-        <v>248</v>
       </c>
       <c r="H80">
         <v>0.16669999999999999</v>
@@ -5560,20 +5588,20 @@
       <c r="B81" s="3">
         <v>45762</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C81" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="D81" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="D81" t="s">
+      <c r="E81" t="s">
+        <v>11</v>
+      </c>
+      <c r="F81" t="s">
+        <v>16</v>
+      </c>
+      <c r="G81" t="s">
         <v>250</v>
-      </c>
-      <c r="E81" t="s">
-        <v>11</v>
-      </c>
-      <c r="F81" t="s">
-        <v>16</v>
-      </c>
-      <c r="G81" t="s">
-        <v>251</v>
       </c>
       <c r="H81">
         <v>0.16669999999999999</v>
@@ -5589,11 +5617,11 @@
       <c r="B82" s="3">
         <v>45762</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C82" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="D82" s="4" t="s">
         <v>252</v>
-      </c>
-      <c r="D82" t="s">
-        <v>253</v>
       </c>
       <c r="E82" t="s">
         <v>11</v>
@@ -5602,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="G82" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H82">
         <v>0.16669999999999999</v>
@@ -5618,20 +5646,20 @@
       <c r="B83" s="3">
         <v>45762</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C83" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="D83" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="D83" t="s">
+      <c r="E83" t="s">
+        <v>11</v>
+      </c>
+      <c r="F83" t="s">
+        <v>16</v>
+      </c>
+      <c r="G83" t="s">
         <v>256</v>
-      </c>
-      <c r="E83" t="s">
-        <v>11</v>
-      </c>
-      <c r="F83" t="s">
-        <v>16</v>
-      </c>
-      <c r="G83" t="s">
-        <v>257</v>
       </c>
       <c r="H83">
         <v>0.16669999999999999</v>
@@ -5647,20 +5675,20 @@
       <c r="B84" s="3">
         <v>45762</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C84" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="D84" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="D84" t="s">
+      <c r="E84" t="s">
+        <v>11</v>
+      </c>
+      <c r="F84" t="s">
+        <v>16</v>
+      </c>
+      <c r="G84" t="s">
         <v>259</v>
-      </c>
-      <c r="E84" t="s">
-        <v>11</v>
-      </c>
-      <c r="F84" t="s">
-        <v>16</v>
-      </c>
-      <c r="G84" t="s">
-        <v>260</v>
       </c>
       <c r="H84">
         <v>0.16669999999999999</v>
@@ -5676,20 +5704,20 @@
       <c r="B85" s="3">
         <v>45762</v>
       </c>
-      <c r="C85" t="s">
+      <c r="C85" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="D85" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="D85" t="s">
+      <c r="E85" t="s">
+        <v>11</v>
+      </c>
+      <c r="F85" t="s">
+        <v>16</v>
+      </c>
+      <c r="G85" t="s">
         <v>262</v>
-      </c>
-      <c r="E85" t="s">
-        <v>11</v>
-      </c>
-      <c r="F85" t="s">
-        <v>16</v>
-      </c>
-      <c r="G85" t="s">
-        <v>263</v>
       </c>
       <c r="H85">
         <v>0.16669999999999999</v>
@@ -5705,11 +5733,11 @@
       <c r="B86" s="3">
         <v>45762</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C86" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="D86" s="4" t="s">
         <v>264</v>
-      </c>
-      <c r="D86" t="s">
-        <v>265</v>
       </c>
       <c r="E86" t="s">
         <v>11</v>
@@ -5718,7 +5746,7 @@
         <v>12</v>
       </c>
       <c r="G86" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H86">
         <v>0.16669999999999999</v>
@@ -5734,11 +5762,11 @@
       <c r="B87" s="3">
         <v>45762</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C87" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="D87" s="4" t="s">
         <v>267</v>
-      </c>
-      <c r="D87" t="s">
-        <v>268</v>
       </c>
       <c r="E87" t="s">
         <v>11</v>
@@ -5747,7 +5775,7 @@
         <v>12</v>
       </c>
       <c r="G87" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H87">
         <v>0.16669999999999999</v>
@@ -5763,11 +5791,11 @@
       <c r="B88" s="3">
         <v>45762</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C88" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D88" s="4" t="s">
         <v>270</v>
-      </c>
-      <c r="D88" t="s">
-        <v>271</v>
       </c>
       <c r="E88" t="s">
         <v>11</v>
@@ -5776,7 +5804,7 @@
         <v>12</v>
       </c>
       <c r="G88" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H88">
         <v>0.16669999999999999</v>
@@ -5792,11 +5820,11 @@
       <c r="B89" s="3">
         <v>45762</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C89" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="D89" s="4" t="s">
         <v>273</v>
-      </c>
-      <c r="D89" t="s">
-        <v>274</v>
       </c>
       <c r="E89" t="s">
         <v>11</v>
@@ -5805,7 +5833,7 @@
         <v>12</v>
       </c>
       <c r="G89" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H89">
         <v>0.16669999999999999</v>
@@ -5821,11 +5849,11 @@
       <c r="B90" s="3">
         <v>45762</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C90" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="D90" s="4" t="s">
         <v>276</v>
-      </c>
-      <c r="D90" t="s">
-        <v>277</v>
       </c>
       <c r="E90" t="s">
         <v>11</v>
@@ -5834,7 +5862,7 @@
         <v>12</v>
       </c>
       <c r="G90" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H90">
         <v>0.16669999999999999</v>
@@ -5850,20 +5878,20 @@
       <c r="B91" s="3">
         <v>45762</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C91" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="D91" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="D91" t="s">
+      <c r="E91" t="s">
+        <v>11</v>
+      </c>
+      <c r="F91" t="s">
+        <v>16</v>
+      </c>
+      <c r="G91" t="s">
         <v>280</v>
-      </c>
-      <c r="E91" t="s">
-        <v>11</v>
-      </c>
-      <c r="F91" t="s">
-        <v>16</v>
-      </c>
-      <c r="G91" t="s">
-        <v>281</v>
       </c>
       <c r="H91">
         <v>0.16669999999999999</v>
@@ -5879,20 +5907,20 @@
       <c r="B92" s="3">
         <v>45762</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C92" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="D92" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="D92" t="s">
+      <c r="E92" t="s">
+        <v>11</v>
+      </c>
+      <c r="F92" t="s">
+        <v>16</v>
+      </c>
+      <c r="G92" t="s">
         <v>283</v>
-      </c>
-      <c r="E92" t="s">
-        <v>11</v>
-      </c>
-      <c r="F92" t="s">
-        <v>16</v>
-      </c>
-      <c r="G92" t="s">
-        <v>284</v>
       </c>
       <c r="H92">
         <v>0.16669999999999999</v>
@@ -5908,11 +5936,11 @@
       <c r="B93" s="3">
         <v>45762</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C93" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="D93" s="4" t="s">
         <v>285</v>
-      </c>
-      <c r="D93" t="s">
-        <v>286</v>
       </c>
       <c r="E93" t="s">
         <v>11</v>
@@ -5921,7 +5949,7 @@
         <v>12</v>
       </c>
       <c r="G93" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H93">
         <v>0.16669999999999999</v>
@@ -5937,20 +5965,20 @@
       <c r="B94" s="3">
         <v>45762</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C94" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="D94" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="D94" t="s">
+      <c r="E94" t="s">
+        <v>11</v>
+      </c>
+      <c r="F94" t="s">
+        <v>16</v>
+      </c>
+      <c r="G94" t="s">
         <v>289</v>
-      </c>
-      <c r="E94" t="s">
-        <v>11</v>
-      </c>
-      <c r="F94" t="s">
-        <v>16</v>
-      </c>
-      <c r="G94" t="s">
-        <v>290</v>
       </c>
       <c r="H94">
         <v>0.16669999999999999</v>
@@ -5966,20 +5994,20 @@
       <c r="B95" s="3">
         <v>45762</v>
       </c>
-      <c r="C95" t="s">
+      <c r="C95" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="D95" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="D95" t="s">
+      <c r="E95" t="s">
+        <v>11</v>
+      </c>
+      <c r="F95" t="s">
+        <v>16</v>
+      </c>
+      <c r="G95" t="s">
         <v>292</v>
-      </c>
-      <c r="E95" t="s">
-        <v>11</v>
-      </c>
-      <c r="F95" t="s">
-        <v>16</v>
-      </c>
-      <c r="G95" t="s">
-        <v>293</v>
       </c>
       <c r="H95">
         <v>0.16669999999999999</v>
@@ -5995,20 +6023,20 @@
       <c r="B96" s="3">
         <v>45762</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C96" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="D96" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="D96" t="s">
+      <c r="E96" t="s">
+        <v>11</v>
+      </c>
+      <c r="F96" t="s">
+        <v>16</v>
+      </c>
+      <c r="G96" t="s">
         <v>295</v>
-      </c>
-      <c r="E96" t="s">
-        <v>11</v>
-      </c>
-      <c r="F96" t="s">
-        <v>16</v>
-      </c>
-      <c r="G96" t="s">
-        <v>296</v>
       </c>
       <c r="H96">
         <v>0.16669999999999999</v>
@@ -6024,11 +6052,11 @@
       <c r="B97" s="3">
         <v>45762</v>
       </c>
-      <c r="C97" t="s">
+      <c r="C97" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="D97" s="4" t="s">
         <v>297</v>
-      </c>
-      <c r="D97" t="s">
-        <v>298</v>
       </c>
       <c r="E97" t="s">
         <v>11</v>
@@ -6037,7 +6065,7 @@
         <v>12</v>
       </c>
       <c r="G97" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H97">
         <v>0.16669999999999999</v>
@@ -6053,11 +6081,11 @@
       <c r="B98" s="3">
         <v>45762</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C98" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="D98" s="4" t="s">
         <v>300</v>
-      </c>
-      <c r="D98" t="s">
-        <v>301</v>
       </c>
       <c r="E98" t="s">
         <v>11</v>
@@ -6066,7 +6094,7 @@
         <v>12</v>
       </c>
       <c r="G98" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H98">
         <v>0.16669999999999999</v>
@@ -6082,11 +6110,11 @@
       <c r="B99" s="3">
         <v>45762</v>
       </c>
-      <c r="C99" t="s">
+      <c r="C99" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="D99" s="4" t="s">
         <v>303</v>
-      </c>
-      <c r="D99" t="s">
-        <v>304</v>
       </c>
       <c r="E99" t="s">
         <v>11</v>
@@ -6095,7 +6123,7 @@
         <v>12</v>
       </c>
       <c r="G99" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H99">
         <v>0.16669999999999999</v>
@@ -6111,11 +6139,11 @@
       <c r="B100" s="3">
         <v>45762</v>
       </c>
-      <c r="C100" t="s">
+      <c r="C100" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="D100" s="4" t="s">
         <v>306</v>
-      </c>
-      <c r="D100" t="s">
-        <v>307</v>
       </c>
       <c r="E100" t="s">
         <v>11</v>
@@ -6124,7 +6152,7 @@
         <v>12</v>
       </c>
       <c r="G100" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H100">
         <v>0.16669999999999999</v>
@@ -6140,20 +6168,20 @@
       <c r="B101" s="3">
         <v>45762</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C101" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="D101" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="D101" t="s">
+      <c r="E101" t="s">
+        <v>11</v>
+      </c>
+      <c r="F101" t="s">
+        <v>16</v>
+      </c>
+      <c r="G101" t="s">
         <v>310</v>
-      </c>
-      <c r="E101" t="s">
-        <v>11</v>
-      </c>
-      <c r="F101" t="s">
-        <v>16</v>
-      </c>
-      <c r="G101" t="s">
-        <v>311</v>
       </c>
       <c r="H101">
         <v>0.16669999999999999</v>
@@ -6169,20 +6197,20 @@
       <c r="B102" s="3">
         <v>45762</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C102" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="D102" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="D102" t="s">
+      <c r="E102" t="s">
+        <v>11</v>
+      </c>
+      <c r="F102" t="s">
+        <v>16</v>
+      </c>
+      <c r="G102" t="s">
         <v>313</v>
-      </c>
-      <c r="E102" t="s">
-        <v>11</v>
-      </c>
-      <c r="F102" t="s">
-        <v>16</v>
-      </c>
-      <c r="G102" t="s">
-        <v>314</v>
       </c>
       <c r="H102">
         <v>0.16669999999999999</v>
@@ -6198,20 +6226,20 @@
       <c r="B103" s="3">
         <v>45762</v>
       </c>
-      <c r="C103" t="s">
+      <c r="C103" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="D103" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="D103" t="s">
+      <c r="E103" t="s">
+        <v>11</v>
+      </c>
+      <c r="F103" t="s">
+        <v>16</v>
+      </c>
+      <c r="G103" t="s">
         <v>316</v>
-      </c>
-      <c r="E103" t="s">
-        <v>11</v>
-      </c>
-      <c r="F103" t="s">
-        <v>16</v>
-      </c>
-      <c r="G103" t="s">
-        <v>317</v>
       </c>
       <c r="H103">
         <v>0.16669999999999999</v>
@@ -6227,11 +6255,11 @@
       <c r="B104" s="3">
         <v>45762</v>
       </c>
-      <c r="C104" t="s">
+      <c r="C104" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="D104" s="4" t="s">
         <v>318</v>
-      </c>
-      <c r="D104" t="s">
-        <v>319</v>
       </c>
       <c r="E104" t="s">
         <v>11</v>
@@ -6240,7 +6268,7 @@
         <v>12</v>
       </c>
       <c r="G104" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H104">
         <v>0.16669999999999999</v>
@@ -6256,11 +6284,11 @@
       <c r="B105" s="3">
         <v>45762</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C105" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="D105" s="4" t="s">
         <v>321</v>
-      </c>
-      <c r="D105" t="s">
-        <v>322</v>
       </c>
       <c r="E105" t="s">
         <v>11</v>
@@ -6269,7 +6297,7 @@
         <v>12</v>
       </c>
       <c r="G105" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H105">
         <v>0.16669999999999999</v>
@@ -6285,20 +6313,20 @@
       <c r="B106" s="3">
         <v>45762</v>
       </c>
-      <c r="C106" t="s">
+      <c r="C106" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="D106" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="D106" t="s">
+      <c r="E106" t="s">
+        <v>11</v>
+      </c>
+      <c r="F106" t="s">
+        <v>16</v>
+      </c>
+      <c r="G106" t="s">
         <v>325</v>
-      </c>
-      <c r="E106" t="s">
-        <v>11</v>
-      </c>
-      <c r="F106" t="s">
-        <v>16</v>
-      </c>
-      <c r="G106" t="s">
-        <v>326</v>
       </c>
       <c r="H106">
         <v>0.16669999999999999</v>
@@ -6314,20 +6342,20 @@
       <c r="B107" s="3">
         <v>45762</v>
       </c>
-      <c r="C107" t="s">
+      <c r="C107" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="D107" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="D107" t="s">
+      <c r="E107" t="s">
+        <v>11</v>
+      </c>
+      <c r="F107" t="s">
+        <v>16</v>
+      </c>
+      <c r="G107" t="s">
         <v>328</v>
-      </c>
-      <c r="E107" t="s">
-        <v>11</v>
-      </c>
-      <c r="F107" t="s">
-        <v>16</v>
-      </c>
-      <c r="G107" t="s">
-        <v>329</v>
       </c>
       <c r="H107">
         <v>0.16669999999999999</v>
@@ -6343,11 +6371,11 @@
       <c r="B108" s="3">
         <v>45762</v>
       </c>
-      <c r="C108" t="s">
+      <c r="C108" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="D108" s="4" t="s">
         <v>330</v>
-      </c>
-      <c r="D108" t="s">
-        <v>331</v>
       </c>
       <c r="E108" t="s">
         <v>11</v>
@@ -6356,7 +6384,7 @@
         <v>12</v>
       </c>
       <c r="G108" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H108">
         <v>0.16669999999999999</v>
@@ -6372,20 +6400,20 @@
       <c r="B109" s="3">
         <v>45762</v>
       </c>
-      <c r="C109" t="s">
+      <c r="C109" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="D109" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="D109" t="s">
+      <c r="E109" t="s">
+        <v>11</v>
+      </c>
+      <c r="F109" t="s">
+        <v>16</v>
+      </c>
+      <c r="G109" t="s">
         <v>334</v>
-      </c>
-      <c r="E109" t="s">
-        <v>11</v>
-      </c>
-      <c r="F109" t="s">
-        <v>16</v>
-      </c>
-      <c r="G109" t="s">
-        <v>335</v>
       </c>
       <c r="H109">
         <v>0.16669999999999999</v>
@@ -6401,20 +6429,20 @@
       <c r="B110" s="3">
         <v>45762</v>
       </c>
-      <c r="C110" t="s">
+      <c r="C110" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="D110" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="D110" t="s">
+      <c r="E110" t="s">
+        <v>11</v>
+      </c>
+      <c r="F110" t="s">
+        <v>16</v>
+      </c>
+      <c r="G110" t="s">
         <v>337</v>
-      </c>
-      <c r="E110" t="s">
-        <v>11</v>
-      </c>
-      <c r="F110" t="s">
-        <v>16</v>
-      </c>
-      <c r="G110" t="s">
-        <v>338</v>
       </c>
       <c r="H110">
         <v>0.16669999999999999</v>
@@ -6430,20 +6458,20 @@
       <c r="B111" s="3">
         <v>45762</v>
       </c>
-      <c r="C111" t="s">
+      <c r="C111" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="D111" s="4" t="s">
         <v>339</v>
       </c>
-      <c r="D111" t="s">
+      <c r="E111" t="s">
+        <v>11</v>
+      </c>
+      <c r="F111" t="s">
+        <v>16</v>
+      </c>
+      <c r="G111" t="s">
         <v>340</v>
-      </c>
-      <c r="E111" t="s">
-        <v>11</v>
-      </c>
-      <c r="F111" t="s">
-        <v>16</v>
-      </c>
-      <c r="G111" t="s">
-        <v>341</v>
       </c>
       <c r="H111">
         <v>0.16669999999999999</v>
@@ -6459,20 +6487,20 @@
       <c r="B112" s="3">
         <v>45762</v>
       </c>
-      <c r="C112" t="s">
+      <c r="C112" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="D112" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="D112" t="s">
+      <c r="E112" t="s">
+        <v>11</v>
+      </c>
+      <c r="F112" t="s">
+        <v>16</v>
+      </c>
+      <c r="G112" t="s">
         <v>343</v>
-      </c>
-      <c r="E112" t="s">
-        <v>11</v>
-      </c>
-      <c r="F112" t="s">
-        <v>16</v>
-      </c>
-      <c r="G112" t="s">
-        <v>344</v>
       </c>
       <c r="H112">
         <v>0.16669999999999999</v>
@@ -6488,20 +6516,20 @@
       <c r="B113" s="3">
         <v>45762</v>
       </c>
-      <c r="C113" t="s">
+      <c r="C113" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="D113" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="D113" t="s">
+      <c r="E113" t="s">
+        <v>11</v>
+      </c>
+      <c r="F113" t="s">
+        <v>16</v>
+      </c>
+      <c r="G113" t="s">
         <v>346</v>
-      </c>
-      <c r="E113" t="s">
-        <v>11</v>
-      </c>
-      <c r="F113" t="s">
-        <v>16</v>
-      </c>
-      <c r="G113" t="s">
-        <v>347</v>
       </c>
       <c r="H113">
         <v>0.16669999999999999</v>
@@ -6517,20 +6545,20 @@
       <c r="B114" s="3">
         <v>45762</v>
       </c>
-      <c r="C114" t="s">
+      <c r="C114" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="D114" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="D114" t="s">
+      <c r="E114" t="s">
+        <v>11</v>
+      </c>
+      <c r="F114" t="s">
+        <v>16</v>
+      </c>
+      <c r="G114" t="s">
         <v>349</v>
-      </c>
-      <c r="E114" t="s">
-        <v>11</v>
-      </c>
-      <c r="F114" t="s">
-        <v>16</v>
-      </c>
-      <c r="G114" t="s">
-        <v>350</v>
       </c>
       <c r="H114">
         <v>0.16669999999999999</v>
@@ -6546,11 +6574,11 @@
       <c r="B115" s="3">
         <v>45762</v>
       </c>
-      <c r="C115" t="s">
+      <c r="C115" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="D115" s="4" t="s">
         <v>351</v>
-      </c>
-      <c r="D115" t="s">
-        <v>352</v>
       </c>
       <c r="E115" t="s">
         <v>11</v>
@@ -6559,7 +6587,7 @@
         <v>12</v>
       </c>
       <c r="G115" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H115">
         <v>0.16669999999999999</v>
@@ -6575,11 +6603,11 @@
       <c r="B116" s="3">
         <v>45762</v>
       </c>
-      <c r="C116" t="s">
+      <c r="C116" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="D116" s="4" t="s">
         <v>354</v>
-      </c>
-      <c r="D116" t="s">
-        <v>355</v>
       </c>
       <c r="E116" t="s">
         <v>11</v>
@@ -6588,7 +6616,7 @@
         <v>12</v>
       </c>
       <c r="G116" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H116">
         <v>0.16669999999999999</v>
@@ -6604,11 +6632,11 @@
       <c r="B117" s="3">
         <v>45762</v>
       </c>
-      <c r="C117" t="s">
+      <c r="C117" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="D117" s="4" t="s">
         <v>357</v>
-      </c>
-      <c r="D117" t="s">
-        <v>358</v>
       </c>
       <c r="E117" t="s">
         <v>11</v>
@@ -6617,7 +6645,7 @@
         <v>12</v>
       </c>
       <c r="G117" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H117">
         <v>0.16669999999999999</v>
@@ -6633,20 +6661,20 @@
       <c r="B118" s="3">
         <v>45762</v>
       </c>
-      <c r="C118" t="s">
+      <c r="C118" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="D118" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="D118" t="s">
+      <c r="E118" t="s">
+        <v>11</v>
+      </c>
+      <c r="F118" t="s">
+        <v>16</v>
+      </c>
+      <c r="G118" t="s">
         <v>361</v>
-      </c>
-      <c r="E118" t="s">
-        <v>11</v>
-      </c>
-      <c r="F118" t="s">
-        <v>16</v>
-      </c>
-      <c r="G118" t="s">
-        <v>362</v>
       </c>
       <c r="H118">
         <v>0.16669999999999999</v>
@@ -6662,11 +6690,11 @@
       <c r="B119" s="3">
         <v>45762</v>
       </c>
-      <c r="C119" t="s">
+      <c r="C119" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D119" s="4" t="s">
         <v>363</v>
-      </c>
-      <c r="D119" t="s">
-        <v>364</v>
       </c>
       <c r="E119" t="s">
         <v>11</v>
@@ -6675,7 +6703,7 @@
         <v>12</v>
       </c>
       <c r="G119" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H119">
         <v>0.16669999999999999</v>
@@ -6691,11 +6719,11 @@
       <c r="B120" s="3">
         <v>45762</v>
       </c>
-      <c r="C120" t="s">
+      <c r="C120" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="D120" s="4" t="s">
         <v>366</v>
-      </c>
-      <c r="D120" t="s">
-        <v>367</v>
       </c>
       <c r="E120" t="s">
         <v>11</v>
@@ -6704,7 +6732,7 @@
         <v>12</v>
       </c>
       <c r="G120" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H120">
         <v>0.16669999999999999</v>
@@ -6720,11 +6748,11 @@
       <c r="B121" s="3">
         <v>45762</v>
       </c>
-      <c r="C121" t="s">
-        <v>369</v>
-      </c>
-      <c r="D121" t="s">
-        <v>370</v>
+      <c r="C121" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>944</v>
       </c>
       <c r="E121" t="s">
         <v>11</v>
@@ -6733,7 +6761,7 @@
         <v>12</v>
       </c>
       <c r="G121" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="H121">
         <v>0.16669999999999999</v>
@@ -6749,11 +6777,11 @@
       <c r="B122" s="3">
         <v>45762</v>
       </c>
-      <c r="C122" t="s">
-        <v>372</v>
-      </c>
-      <c r="D122" t="s">
-        <v>373</v>
+      <c r="C122" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="D122" s="4" t="s">
+        <v>371</v>
       </c>
       <c r="E122" t="s">
         <v>11</v>
@@ -6762,7 +6790,7 @@
         <v>12</v>
       </c>
       <c r="G122" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="H122">
         <v>0.16669999999999999</v>
@@ -6778,20 +6806,20 @@
       <c r="B123" s="3">
         <v>45762</v>
       </c>
-      <c r="C123" t="s">
+      <c r="C123" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="D123" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="E123" t="s">
+        <v>11</v>
+      </c>
+      <c r="F123" t="s">
+        <v>16</v>
+      </c>
+      <c r="G123" t="s">
         <v>375</v>
-      </c>
-      <c r="D123" t="s">
-        <v>376</v>
-      </c>
-      <c r="E123" t="s">
-        <v>11</v>
-      </c>
-      <c r="F123" t="s">
-        <v>16</v>
-      </c>
-      <c r="G123" t="s">
-        <v>377</v>
       </c>
       <c r="H123">
         <v>0.16669999999999999</v>
@@ -6807,11 +6835,11 @@
       <c r="B124" s="3">
         <v>45762</v>
       </c>
-      <c r="C124" t="s">
-        <v>378</v>
-      </c>
-      <c r="D124" t="s">
-        <v>379</v>
+      <c r="C124" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="D124" s="4" t="s">
+        <v>377</v>
       </c>
       <c r="E124" t="s">
         <v>11</v>
@@ -6820,7 +6848,7 @@
         <v>12</v>
       </c>
       <c r="G124" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="H124">
         <v>0.16669999999999999</v>
@@ -6836,20 +6864,20 @@
       <c r="B125" s="3">
         <v>45762</v>
       </c>
-      <c r="C125" t="s">
+      <c r="C125" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="D125" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="E125" t="s">
+        <v>11</v>
+      </c>
+      <c r="F125" t="s">
+        <v>16</v>
+      </c>
+      <c r="G125" t="s">
         <v>381</v>
-      </c>
-      <c r="D125" t="s">
-        <v>382</v>
-      </c>
-      <c r="E125" t="s">
-        <v>11</v>
-      </c>
-      <c r="F125" t="s">
-        <v>16</v>
-      </c>
-      <c r="G125" t="s">
-        <v>383</v>
       </c>
       <c r="H125">
         <v>0.16669999999999999</v>
@@ -6865,20 +6893,20 @@
       <c r="B126" s="3">
         <v>45762</v>
       </c>
-      <c r="C126" t="s">
+      <c r="C126" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="D126" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="E126" t="s">
+        <v>11</v>
+      </c>
+      <c r="F126" t="s">
+        <v>16</v>
+      </c>
+      <c r="G126" t="s">
         <v>384</v>
-      </c>
-      <c r="D126" t="s">
-        <v>385</v>
-      </c>
-      <c r="E126" t="s">
-        <v>11</v>
-      </c>
-      <c r="F126" t="s">
-        <v>16</v>
-      </c>
-      <c r="G126" t="s">
-        <v>386</v>
       </c>
       <c r="H126">
         <v>0.16669999999999999</v>
@@ -6894,11 +6922,11 @@
       <c r="B127" s="3">
         <v>45762</v>
       </c>
-      <c r="C127" t="s">
-        <v>387</v>
-      </c>
-      <c r="D127" t="s">
-        <v>388</v>
+      <c r="C127" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="D127" s="4" t="s">
+        <v>386</v>
       </c>
       <c r="E127" t="s">
         <v>11</v>
@@ -6907,7 +6935,7 @@
         <v>12</v>
       </c>
       <c r="G127" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H127">
         <v>0.16669999999999999</v>
@@ -6923,20 +6951,20 @@
       <c r="B128" s="3">
         <v>45762</v>
       </c>
-      <c r="C128" t="s">
+      <c r="C128" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="D128" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="E128" t="s">
+        <v>11</v>
+      </c>
+      <c r="F128" t="s">
+        <v>16</v>
+      </c>
+      <c r="G128" t="s">
         <v>390</v>
-      </c>
-      <c r="D128" t="s">
-        <v>391</v>
-      </c>
-      <c r="E128" t="s">
-        <v>11</v>
-      </c>
-      <c r="F128" t="s">
-        <v>16</v>
-      </c>
-      <c r="G128" t="s">
-        <v>392</v>
       </c>
       <c r="H128">
         <v>0.16669999999999999</v>
@@ -6952,20 +6980,20 @@
       <c r="B129" s="3">
         <v>45762</v>
       </c>
-      <c r="C129" t="s">
+      <c r="C129" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="D129" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="E129" t="s">
+        <v>11</v>
+      </c>
+      <c r="F129" t="s">
+        <v>16</v>
+      </c>
+      <c r="G129" t="s">
         <v>393</v>
-      </c>
-      <c r="D129" t="s">
-        <v>394</v>
-      </c>
-      <c r="E129" t="s">
-        <v>11</v>
-      </c>
-      <c r="F129" t="s">
-        <v>16</v>
-      </c>
-      <c r="G129" t="s">
-        <v>395</v>
       </c>
       <c r="H129">
         <v>0.16669999999999999</v>
@@ -6981,11 +7009,11 @@
       <c r="B130" s="3">
         <v>45762</v>
       </c>
-      <c r="C130" t="s">
-        <v>396</v>
-      </c>
-      <c r="D130" t="s">
-        <v>397</v>
+      <c r="C130" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="D130" s="4" t="s">
+        <v>395</v>
       </c>
       <c r="E130" t="s">
         <v>11</v>
@@ -6994,7 +7022,7 @@
         <v>12</v>
       </c>
       <c r="G130" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="H130">
         <v>0.16669999999999999</v>
@@ -7010,20 +7038,20 @@
       <c r="B131" s="3">
         <v>45762</v>
       </c>
-      <c r="C131" t="s">
+      <c r="C131" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="D131" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="E131" t="s">
+        <v>11</v>
+      </c>
+      <c r="F131" t="s">
+        <v>16</v>
+      </c>
+      <c r="G131" t="s">
         <v>399</v>
-      </c>
-      <c r="D131" t="s">
-        <v>400</v>
-      </c>
-      <c r="E131" t="s">
-        <v>11</v>
-      </c>
-      <c r="F131" t="s">
-        <v>16</v>
-      </c>
-      <c r="G131" t="s">
-        <v>401</v>
       </c>
       <c r="H131">
         <v>0.16669999999999999</v>
@@ -7039,11 +7067,11 @@
       <c r="B132" s="3">
         <v>45762</v>
       </c>
-      <c r="C132" t="s">
-        <v>402</v>
-      </c>
-      <c r="D132" t="s">
-        <v>403</v>
+      <c r="C132" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="D132" s="4" t="s">
+        <v>401</v>
       </c>
       <c r="E132" t="s">
         <v>11</v>
@@ -7052,7 +7080,7 @@
         <v>12</v>
       </c>
       <c r="G132" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="H132">
         <v>0.16669999999999999</v>
@@ -7068,20 +7096,20 @@
       <c r="B133" s="3">
         <v>45762</v>
       </c>
-      <c r="C133" t="s">
+      <c r="C133" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="D133" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="E133" t="s">
+        <v>11</v>
+      </c>
+      <c r="F133" t="s">
+        <v>16</v>
+      </c>
+      <c r="G133" t="s">
         <v>405</v>
-      </c>
-      <c r="D133" t="s">
-        <v>406</v>
-      </c>
-      <c r="E133" t="s">
-        <v>11</v>
-      </c>
-      <c r="F133" t="s">
-        <v>16</v>
-      </c>
-      <c r="G133" t="s">
-        <v>407</v>
       </c>
       <c r="H133">
         <v>0.16669999999999999</v>
@@ -7097,20 +7125,20 @@
       <c r="B134" s="3">
         <v>45762</v>
       </c>
-      <c r="C134" t="s">
+      <c r="C134" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="D134" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="E134" t="s">
+        <v>11</v>
+      </c>
+      <c r="F134" t="s">
+        <v>16</v>
+      </c>
+      <c r="G134" t="s">
         <v>408</v>
-      </c>
-      <c r="D134" t="s">
-        <v>409</v>
-      </c>
-      <c r="E134" t="s">
-        <v>11</v>
-      </c>
-      <c r="F134" t="s">
-        <v>16</v>
-      </c>
-      <c r="G134" t="s">
-        <v>410</v>
       </c>
       <c r="H134">
         <v>0.16669999999999999</v>
@@ -7126,11 +7154,11 @@
       <c r="B135" s="3">
         <v>45762</v>
       </c>
-      <c r="C135" t="s">
-        <v>411</v>
-      </c>
-      <c r="D135" t="s">
-        <v>412</v>
+      <c r="C135" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="D135" s="4" t="s">
+        <v>410</v>
       </c>
       <c r="E135" t="s">
         <v>11</v>
@@ -7139,7 +7167,7 @@
         <v>12</v>
       </c>
       <c r="G135" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="H135">
         <v>0.16669999999999999</v>
@@ -7155,11 +7183,11 @@
       <c r="B136" s="3">
         <v>45762</v>
       </c>
-      <c r="C136" t="s">
-        <v>414</v>
-      </c>
-      <c r="D136" t="s">
-        <v>415</v>
+      <c r="C136" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="D136" s="4" t="s">
+        <v>413</v>
       </c>
       <c r="E136" t="s">
         <v>11</v>
@@ -7168,7 +7196,7 @@
         <v>12</v>
       </c>
       <c r="G136" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="H136">
         <v>0.16669999999999999</v>
@@ -7184,20 +7212,20 @@
       <c r="B137" s="3">
         <v>45762</v>
       </c>
-      <c r="C137" t="s">
+      <c r="C137" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="D137" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="E137" t="s">
+        <v>11</v>
+      </c>
+      <c r="F137" t="s">
+        <v>16</v>
+      </c>
+      <c r="G137" t="s">
         <v>417</v>
-      </c>
-      <c r="D137" t="s">
-        <v>418</v>
-      </c>
-      <c r="E137" t="s">
-        <v>11</v>
-      </c>
-      <c r="F137" t="s">
-        <v>16</v>
-      </c>
-      <c r="G137" t="s">
-        <v>419</v>
       </c>
       <c r="H137">
         <v>0.16669999999999999</v>
@@ -7213,20 +7241,20 @@
       <c r="B138" s="3">
         <v>45762</v>
       </c>
-      <c r="C138" t="s">
+      <c r="C138" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="D138" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="E138" t="s">
+        <v>11</v>
+      </c>
+      <c r="F138" t="s">
+        <v>16</v>
+      </c>
+      <c r="G138" t="s">
         <v>420</v>
-      </c>
-      <c r="D138" t="s">
-        <v>421</v>
-      </c>
-      <c r="E138" t="s">
-        <v>11</v>
-      </c>
-      <c r="F138" t="s">
-        <v>16</v>
-      </c>
-      <c r="G138" t="s">
-        <v>422</v>
       </c>
       <c r="H138">
         <v>0.16669999999999999</v>
@@ -7242,11 +7270,11 @@
       <c r="B139" s="3">
         <v>45762</v>
       </c>
-      <c r="C139" t="s">
-        <v>423</v>
-      </c>
-      <c r="D139" t="s">
-        <v>424</v>
+      <c r="C139" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="D139" s="4" t="s">
+        <v>422</v>
       </c>
       <c r="E139" t="s">
         <v>11</v>
@@ -7255,7 +7283,7 @@
         <v>12</v>
       </c>
       <c r="G139" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H139">
         <v>0.16669999999999999</v>
@@ -7271,20 +7299,20 @@
       <c r="B140" s="3">
         <v>45762</v>
       </c>
-      <c r="C140" t="s">
+      <c r="C140" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="D140" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="E140" t="s">
+        <v>11</v>
+      </c>
+      <c r="F140" t="s">
+        <v>16</v>
+      </c>
+      <c r="G140" t="s">
         <v>426</v>
-      </c>
-      <c r="D140" t="s">
-        <v>427</v>
-      </c>
-      <c r="E140" t="s">
-        <v>11</v>
-      </c>
-      <c r="F140" t="s">
-        <v>16</v>
-      </c>
-      <c r="G140" t="s">
-        <v>428</v>
       </c>
       <c r="H140">
         <v>0.16669999999999999</v>
@@ -7300,20 +7328,20 @@
       <c r="B141" s="3">
         <v>45762</v>
       </c>
-      <c r="C141" t="s">
+      <c r="C141" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="D141" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="E141" t="s">
+        <v>11</v>
+      </c>
+      <c r="F141" t="s">
+        <v>16</v>
+      </c>
+      <c r="G141" t="s">
         <v>429</v>
-      </c>
-      <c r="D141" t="s">
-        <v>430</v>
-      </c>
-      <c r="E141" t="s">
-        <v>11</v>
-      </c>
-      <c r="F141" t="s">
-        <v>16</v>
-      </c>
-      <c r="G141" t="s">
-        <v>431</v>
       </c>
       <c r="H141">
         <v>0.16669999999999999</v>
@@ -7329,11 +7357,11 @@
       <c r="B142" s="3">
         <v>45762</v>
       </c>
-      <c r="C142" t="s">
-        <v>432</v>
-      </c>
-      <c r="D142" t="s">
-        <v>433</v>
+      <c r="C142" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="D142" s="4" t="s">
+        <v>431</v>
       </c>
       <c r="E142" t="s">
         <v>11</v>
@@ -7342,7 +7370,7 @@
         <v>12</v>
       </c>
       <c r="G142" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="H142">
         <v>0.16669999999999999</v>
@@ -7358,11 +7386,11 @@
       <c r="B143" s="3">
         <v>45762</v>
       </c>
-      <c r="C143" t="s">
-        <v>435</v>
-      </c>
-      <c r="D143" t="s">
-        <v>436</v>
+      <c r="C143" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="D143" s="4" t="s">
+        <v>434</v>
       </c>
       <c r="E143" t="s">
         <v>11</v>
@@ -7371,7 +7399,7 @@
         <v>12</v>
       </c>
       <c r="G143" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="H143">
         <v>0.16669999999999999</v>
@@ -7387,20 +7415,20 @@
       <c r="B144" s="3">
         <v>45762</v>
       </c>
-      <c r="C144" t="s">
+      <c r="C144" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="D144" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="E144" t="s">
+        <v>11</v>
+      </c>
+      <c r="F144" t="s">
+        <v>16</v>
+      </c>
+      <c r="G144" t="s">
         <v>438</v>
-      </c>
-      <c r="D144" t="s">
-        <v>439</v>
-      </c>
-      <c r="E144" t="s">
-        <v>11</v>
-      </c>
-      <c r="F144" t="s">
-        <v>16</v>
-      </c>
-      <c r="G144" t="s">
-        <v>440</v>
       </c>
       <c r="H144">
         <v>0.16669999999999999</v>
@@ -7416,11 +7444,11 @@
       <c r="B145" s="3">
         <v>45762</v>
       </c>
-      <c r="C145" t="s">
-        <v>441</v>
-      </c>
-      <c r="D145" t="s">
-        <v>442</v>
+      <c r="C145" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="D145" s="4" t="s">
+        <v>440</v>
       </c>
       <c r="E145" t="s">
         <v>11</v>
@@ -7429,7 +7457,7 @@
         <v>12</v>
       </c>
       <c r="G145" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="H145">
         <v>0.16669999999999999</v>
@@ -7445,11 +7473,11 @@
       <c r="B146" s="3">
         <v>45762</v>
       </c>
-      <c r="C146" t="s">
-        <v>444</v>
-      </c>
-      <c r="D146" t="s">
-        <v>445</v>
+      <c r="C146" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="D146" s="4" t="s">
+        <v>443</v>
       </c>
       <c r="E146" t="s">
         <v>11</v>
@@ -7458,7 +7486,7 @@
         <v>12</v>
       </c>
       <c r="G146" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="H146">
         <v>0.16669999999999999</v>
@@ -7474,20 +7502,20 @@
       <c r="B147" s="3">
         <v>45762</v>
       </c>
-      <c r="C147" t="s">
+      <c r="C147" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="D147" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="E147" t="s">
+        <v>11</v>
+      </c>
+      <c r="F147" t="s">
+        <v>16</v>
+      </c>
+      <c r="G147" t="s">
         <v>447</v>
-      </c>
-      <c r="D147" t="s">
-        <v>448</v>
-      </c>
-      <c r="E147" t="s">
-        <v>11</v>
-      </c>
-      <c r="F147" t="s">
-        <v>16</v>
-      </c>
-      <c r="G147" t="s">
-        <v>449</v>
       </c>
       <c r="H147">
         <v>0.16669999999999999</v>
@@ -7503,11 +7531,11 @@
       <c r="B148" s="3">
         <v>45762</v>
       </c>
-      <c r="C148" t="s">
-        <v>450</v>
-      </c>
-      <c r="D148" t="s">
-        <v>451</v>
+      <c r="C148" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="D148" s="4" t="s">
+        <v>449</v>
       </c>
       <c r="E148" t="s">
         <v>11</v>
@@ -7516,7 +7544,7 @@
         <v>12</v>
       </c>
       <c r="G148" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="H148">
         <v>0.16669999999999999</v>
@@ -7532,20 +7560,20 @@
       <c r="B149" s="3">
         <v>45762</v>
       </c>
-      <c r="C149" t="s">
+      <c r="C149" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="D149" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="E149" t="s">
+        <v>11</v>
+      </c>
+      <c r="F149" t="s">
+        <v>16</v>
+      </c>
+      <c r="G149" t="s">
         <v>453</v>
-      </c>
-      <c r="D149" t="s">
-        <v>454</v>
-      </c>
-      <c r="E149" t="s">
-        <v>11</v>
-      </c>
-      <c r="F149" t="s">
-        <v>16</v>
-      </c>
-      <c r="G149" t="s">
-        <v>455</v>
       </c>
       <c r="H149">
         <v>0.16669999999999999</v>
@@ -7561,11 +7589,11 @@
       <c r="B150" s="3">
         <v>45762</v>
       </c>
-      <c r="C150" t="s">
-        <v>456</v>
-      </c>
-      <c r="D150" t="s">
-        <v>457</v>
+      <c r="C150" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="D150" s="4" t="s">
+        <v>455</v>
       </c>
       <c r="E150" t="s">
         <v>11</v>
@@ -7574,7 +7602,7 @@
         <v>12</v>
       </c>
       <c r="G150" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="H150">
         <v>0.16669999999999999</v>
@@ -7590,11 +7618,11 @@
       <c r="B151" s="3">
         <v>45762</v>
       </c>
-      <c r="C151" t="s">
-        <v>459</v>
-      </c>
-      <c r="D151" t="s">
-        <v>460</v>
+      <c r="C151" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="D151" s="4" t="s">
+        <v>458</v>
       </c>
       <c r="E151" t="s">
         <v>11</v>
@@ -7603,7 +7631,7 @@
         <v>12</v>
       </c>
       <c r="G151" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H151">
         <v>0.16669999999999999</v>
@@ -7619,20 +7647,20 @@
       <c r="B152" s="3">
         <v>45762</v>
       </c>
-      <c r="C152" t="s">
+      <c r="C152" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="D152" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="E152" t="s">
+        <v>11</v>
+      </c>
+      <c r="F152" t="s">
+        <v>16</v>
+      </c>
+      <c r="G152" t="s">
         <v>462</v>
-      </c>
-      <c r="D152" t="s">
-        <v>463</v>
-      </c>
-      <c r="E152" t="s">
-        <v>11</v>
-      </c>
-      <c r="F152" t="s">
-        <v>16</v>
-      </c>
-      <c r="G152" t="s">
-        <v>464</v>
       </c>
       <c r="H152">
         <v>0.16669999999999999</v>
@@ -7648,20 +7676,20 @@
       <c r="B153" s="3">
         <v>45762</v>
       </c>
-      <c r="C153" t="s">
+      <c r="C153" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="D153" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="E153" t="s">
+        <v>11</v>
+      </c>
+      <c r="F153" t="s">
+        <v>16</v>
+      </c>
+      <c r="G153" t="s">
         <v>465</v>
-      </c>
-      <c r="D153" t="s">
-        <v>466</v>
-      </c>
-      <c r="E153" t="s">
-        <v>11</v>
-      </c>
-      <c r="F153" t="s">
-        <v>16</v>
-      </c>
-      <c r="G153" t="s">
-        <v>467</v>
       </c>
       <c r="H153">
         <v>0.16669999999999999</v>
@@ -7677,11 +7705,11 @@
       <c r="B154" s="3">
         <v>45762</v>
       </c>
-      <c r="C154" t="s">
-        <v>468</v>
-      </c>
-      <c r="D154" t="s">
-        <v>469</v>
+      <c r="C154" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="D154" s="4" t="s">
+        <v>467</v>
       </c>
       <c r="E154" t="s">
         <v>11</v>
@@ -7690,7 +7718,7 @@
         <v>12</v>
       </c>
       <c r="G154" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="H154">
         <v>0.16669999999999999</v>
@@ -7706,20 +7734,20 @@
       <c r="B155" s="3">
         <v>45762</v>
       </c>
-      <c r="C155" t="s">
+      <c r="C155" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="D155" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="E155" t="s">
+        <v>11</v>
+      </c>
+      <c r="F155" t="s">
+        <v>16</v>
+      </c>
+      <c r="G155" t="s">
         <v>471</v>
-      </c>
-      <c r="D155" t="s">
-        <v>472</v>
-      </c>
-      <c r="E155" t="s">
-        <v>11</v>
-      </c>
-      <c r="F155" t="s">
-        <v>16</v>
-      </c>
-      <c r="G155" t="s">
-        <v>473</v>
       </c>
       <c r="H155">
         <v>0.16669999999999999</v>
@@ -7735,20 +7763,20 @@
       <c r="B156" s="3">
         <v>45762</v>
       </c>
-      <c r="C156" t="s">
+      <c r="C156" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="D156" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="E156" t="s">
+        <v>11</v>
+      </c>
+      <c r="F156" t="s">
+        <v>16</v>
+      </c>
+      <c r="G156" t="s">
         <v>474</v>
-      </c>
-      <c r="D156" t="s">
-        <v>475</v>
-      </c>
-      <c r="E156" t="s">
-        <v>11</v>
-      </c>
-      <c r="F156" t="s">
-        <v>16</v>
-      </c>
-      <c r="G156" t="s">
-        <v>476</v>
       </c>
       <c r="H156">
         <v>0.16669999999999999</v>
@@ -7764,11 +7792,11 @@
       <c r="B157" s="3">
         <v>45762</v>
       </c>
-      <c r="C157" t="s">
-        <v>477</v>
-      </c>
-      <c r="D157" t="s">
-        <v>478</v>
+      <c r="C157" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="D157" s="4" t="s">
+        <v>476</v>
       </c>
       <c r="E157" t="s">
         <v>11</v>
@@ -7777,7 +7805,7 @@
         <v>12</v>
       </c>
       <c r="G157" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="H157">
         <v>0.16669999999999999</v>
@@ -7793,11 +7821,11 @@
       <c r="B158" s="3">
         <v>45762</v>
       </c>
-      <c r="C158" t="s">
-        <v>480</v>
-      </c>
-      <c r="D158" t="s">
-        <v>481</v>
+      <c r="C158" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="D158" s="4" t="s">
+        <v>479</v>
       </c>
       <c r="E158" t="s">
         <v>11</v>
@@ -7806,7 +7834,7 @@
         <v>12</v>
       </c>
       <c r="G158" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="H158">
         <v>0.16669999999999999</v>
@@ -7822,20 +7850,20 @@
       <c r="B159" s="3">
         <v>45762</v>
       </c>
-      <c r="C159" t="s">
+      <c r="C159" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="D159" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="E159" t="s">
+        <v>11</v>
+      </c>
+      <c r="F159" t="s">
+        <v>16</v>
+      </c>
+      <c r="G159" t="s">
         <v>483</v>
-      </c>
-      <c r="D159" t="s">
-        <v>484</v>
-      </c>
-      <c r="E159" t="s">
-        <v>11</v>
-      </c>
-      <c r="F159" t="s">
-        <v>16</v>
-      </c>
-      <c r="G159" t="s">
-        <v>485</v>
       </c>
       <c r="H159">
         <v>0.16669999999999999</v>
@@ -7851,20 +7879,20 @@
       <c r="B160" s="3">
         <v>45762</v>
       </c>
-      <c r="C160" t="s">
+      <c r="C160" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="D160" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="E160" t="s">
+        <v>11</v>
+      </c>
+      <c r="F160" t="s">
+        <v>16</v>
+      </c>
+      <c r="G160" t="s">
         <v>486</v>
-      </c>
-      <c r="D160" t="s">
-        <v>487</v>
-      </c>
-      <c r="E160" t="s">
-        <v>11</v>
-      </c>
-      <c r="F160" t="s">
-        <v>16</v>
-      </c>
-      <c r="G160" t="s">
-        <v>488</v>
       </c>
       <c r="H160">
         <v>0.16669999999999999</v>
@@ -7880,20 +7908,20 @@
       <c r="B161" s="3">
         <v>45762</v>
       </c>
-      <c r="C161" t="s">
+      <c r="C161" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="D161" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="E161" t="s">
+        <v>11</v>
+      </c>
+      <c r="F161" t="s">
+        <v>16</v>
+      </c>
+      <c r="G161" t="s">
         <v>489</v>
-      </c>
-      <c r="D161" t="s">
-        <v>490</v>
-      </c>
-      <c r="E161" t="s">
-        <v>11</v>
-      </c>
-      <c r="F161" t="s">
-        <v>16</v>
-      </c>
-      <c r="G161" t="s">
-        <v>491</v>
       </c>
       <c r="H161">
         <v>0.16669999999999999</v>
@@ -7909,11 +7937,11 @@
       <c r="B162" s="3">
         <v>45762</v>
       </c>
-      <c r="C162" t="s">
-        <v>492</v>
-      </c>
-      <c r="D162" t="s">
-        <v>493</v>
+      <c r="C162" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="D162" s="4" t="s">
+        <v>491</v>
       </c>
       <c r="E162" t="s">
         <v>11</v>
@@ -7922,7 +7950,7 @@
         <v>12</v>
       </c>
       <c r="G162" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="H162">
         <v>0.16669999999999999</v>
@@ -7938,20 +7966,20 @@
       <c r="B163" s="3">
         <v>45762</v>
       </c>
-      <c r="C163" t="s">
+      <c r="C163" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="D163" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="E163" t="s">
+        <v>11</v>
+      </c>
+      <c r="F163" t="s">
+        <v>16</v>
+      </c>
+      <c r="G163" t="s">
         <v>495</v>
-      </c>
-      <c r="D163" t="s">
-        <v>496</v>
-      </c>
-      <c r="E163" t="s">
-        <v>11</v>
-      </c>
-      <c r="F163" t="s">
-        <v>16</v>
-      </c>
-      <c r="G163" t="s">
-        <v>497</v>
       </c>
       <c r="H163">
         <v>0.16669999999999999</v>
@@ -7967,11 +7995,11 @@
       <c r="B164" s="3">
         <v>45762</v>
       </c>
-      <c r="C164" t="s">
-        <v>498</v>
-      </c>
-      <c r="D164" t="s">
-        <v>499</v>
+      <c r="C164" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="D164" s="4" t="s">
+        <v>497</v>
       </c>
       <c r="E164" t="s">
         <v>11</v>
@@ -7980,7 +8008,7 @@
         <v>12</v>
       </c>
       <c r="G164" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="H164">
         <v>0.16669999999999999</v>
@@ -7996,20 +8024,20 @@
       <c r="B165" s="3">
         <v>45762</v>
       </c>
-      <c r="C165" t="s">
+      <c r="C165" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="D165" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="E165" t="s">
+        <v>11</v>
+      </c>
+      <c r="F165" t="s">
+        <v>16</v>
+      </c>
+      <c r="G165" t="s">
         <v>501</v>
-      </c>
-      <c r="D165" t="s">
-        <v>502</v>
-      </c>
-      <c r="E165" t="s">
-        <v>11</v>
-      </c>
-      <c r="F165" t="s">
-        <v>16</v>
-      </c>
-      <c r="G165" t="s">
-        <v>503</v>
       </c>
       <c r="H165">
         <v>0.16669999999999999</v>
@@ -8025,20 +8053,20 @@
       <c r="B166" s="3">
         <v>45762</v>
       </c>
-      <c r="C166" t="s">
+      <c r="C166" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="D166" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="E166" t="s">
+        <v>11</v>
+      </c>
+      <c r="F166" t="s">
+        <v>16</v>
+      </c>
+      <c r="G166" t="s">
         <v>504</v>
-      </c>
-      <c r="D166" t="s">
-        <v>505</v>
-      </c>
-      <c r="E166" t="s">
-        <v>11</v>
-      </c>
-      <c r="F166" t="s">
-        <v>16</v>
-      </c>
-      <c r="G166" t="s">
-        <v>506</v>
       </c>
       <c r="H166">
         <v>0.16669999999999999</v>
@@ -8054,20 +8082,20 @@
       <c r="B167" s="3">
         <v>45762</v>
       </c>
-      <c r="C167" t="s">
+      <c r="C167" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="D167" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="E167" t="s">
+        <v>11</v>
+      </c>
+      <c r="F167" t="s">
+        <v>16</v>
+      </c>
+      <c r="G167" t="s">
         <v>507</v>
-      </c>
-      <c r="D167" t="s">
-        <v>508</v>
-      </c>
-      <c r="E167" t="s">
-        <v>11</v>
-      </c>
-      <c r="F167" t="s">
-        <v>16</v>
-      </c>
-      <c r="G167" t="s">
-        <v>509</v>
       </c>
       <c r="H167">
         <v>0.16669999999999999</v>
@@ -8083,20 +8111,20 @@
       <c r="B168" s="3">
         <v>45762</v>
       </c>
-      <c r="C168" t="s">
+      <c r="C168" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="D168" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="E168" t="s">
+        <v>11</v>
+      </c>
+      <c r="F168" t="s">
+        <v>16</v>
+      </c>
+      <c r="G168" t="s">
         <v>510</v>
-      </c>
-      <c r="D168" t="s">
-        <v>511</v>
-      </c>
-      <c r="E168" t="s">
-        <v>11</v>
-      </c>
-      <c r="F168" t="s">
-        <v>16</v>
-      </c>
-      <c r="G168" t="s">
-        <v>512</v>
       </c>
       <c r="H168">
         <v>0.16669999999999999</v>
@@ -8112,20 +8140,20 @@
       <c r="B169" s="3">
         <v>45762</v>
       </c>
-      <c r="C169" t="s">
+      <c r="C169" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="D169" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="E169" t="s">
+        <v>11</v>
+      </c>
+      <c r="F169" t="s">
+        <v>16</v>
+      </c>
+      <c r="G169" t="s">
         <v>513</v>
-      </c>
-      <c r="D169" t="s">
-        <v>514</v>
-      </c>
-      <c r="E169" t="s">
-        <v>11</v>
-      </c>
-      <c r="F169" t="s">
-        <v>16</v>
-      </c>
-      <c r="G169" t="s">
-        <v>515</v>
       </c>
       <c r="H169">
         <v>0.16669999999999999</v>
@@ -8141,20 +8169,20 @@
       <c r="B170" s="3">
         <v>45762</v>
       </c>
-      <c r="C170" t="s">
+      <c r="C170" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="D170" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="E170" t="s">
+        <v>11</v>
+      </c>
+      <c r="F170" t="s">
+        <v>16</v>
+      </c>
+      <c r="G170" t="s">
         <v>516</v>
-      </c>
-      <c r="D170" t="s">
-        <v>517</v>
-      </c>
-      <c r="E170" t="s">
-        <v>11</v>
-      </c>
-      <c r="F170" t="s">
-        <v>16</v>
-      </c>
-      <c r="G170" t="s">
-        <v>518</v>
       </c>
       <c r="H170">
         <v>0.16669999999999999</v>
@@ -8170,20 +8198,20 @@
       <c r="B171" s="3">
         <v>45762</v>
       </c>
-      <c r="C171" t="s">
+      <c r="C171" s="4" t="s">
+        <v>517</v>
+      </c>
+      <c r="D171" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="E171" t="s">
+        <v>11</v>
+      </c>
+      <c r="F171" t="s">
+        <v>16</v>
+      </c>
+      <c r="G171" t="s">
         <v>519</v>
-      </c>
-      <c r="D171" t="s">
-        <v>520</v>
-      </c>
-      <c r="E171" t="s">
-        <v>11</v>
-      </c>
-      <c r="F171" t="s">
-        <v>16</v>
-      </c>
-      <c r="G171" t="s">
-        <v>521</v>
       </c>
       <c r="H171">
         <v>0.16669999999999999</v>
@@ -8199,11 +8227,11 @@
       <c r="B172" s="3">
         <v>45762</v>
       </c>
-      <c r="C172" t="s">
-        <v>522</v>
-      </c>
-      <c r="D172" t="s">
-        <v>523</v>
+      <c r="C172" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="D172" s="4" t="s">
+        <v>521</v>
       </c>
       <c r="E172" t="s">
         <v>11</v>
@@ -8212,7 +8240,7 @@
         <v>12</v>
       </c>
       <c r="G172" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H172">
         <v>0.16669999999999999</v>
@@ -8228,20 +8256,20 @@
       <c r="B173" s="3">
         <v>45762</v>
       </c>
-      <c r="C173" t="s">
+      <c r="C173" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="D173" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="E173" t="s">
+        <v>11</v>
+      </c>
+      <c r="F173" t="s">
+        <v>16</v>
+      </c>
+      <c r="G173" t="s">
         <v>525</v>
-      </c>
-      <c r="D173" t="s">
-        <v>526</v>
-      </c>
-      <c r="E173" t="s">
-        <v>11</v>
-      </c>
-      <c r="F173" t="s">
-        <v>16</v>
-      </c>
-      <c r="G173" t="s">
-        <v>527</v>
       </c>
       <c r="H173">
         <v>0.16669999999999999</v>
@@ -8257,20 +8285,20 @@
       <c r="B174" s="3">
         <v>45762</v>
       </c>
-      <c r="C174" t="s">
+      <c r="C174" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="D174" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="E174" t="s">
+        <v>11</v>
+      </c>
+      <c r="F174" t="s">
+        <v>16</v>
+      </c>
+      <c r="G174" t="s">
         <v>528</v>
-      </c>
-      <c r="D174" t="s">
-        <v>529</v>
-      </c>
-      <c r="E174" t="s">
-        <v>11</v>
-      </c>
-      <c r="F174" t="s">
-        <v>16</v>
-      </c>
-      <c r="G174" t="s">
-        <v>530</v>
       </c>
       <c r="H174">
         <v>0.16669999999999999</v>
@@ -8286,11 +8314,11 @@
       <c r="B175" s="3">
         <v>45762</v>
       </c>
-      <c r="C175" t="s">
-        <v>531</v>
-      </c>
-      <c r="D175" t="s">
-        <v>532</v>
+      <c r="C175" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="D175" s="4" t="s">
+        <v>530</v>
       </c>
       <c r="E175" t="s">
         <v>11</v>
@@ -8299,7 +8327,7 @@
         <v>12</v>
       </c>
       <c r="G175" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="H175">
         <v>0.16669999999999999</v>
@@ -8315,20 +8343,20 @@
       <c r="B176" s="3">
         <v>45762</v>
       </c>
-      <c r="C176" t="s">
+      <c r="C176" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="D176" s="4" t="s">
+        <v>533</v>
+      </c>
+      <c r="E176" t="s">
+        <v>11</v>
+      </c>
+      <c r="F176" t="s">
+        <v>16</v>
+      </c>
+      <c r="G176" t="s">
         <v>534</v>
-      </c>
-      <c r="D176" t="s">
-        <v>535</v>
-      </c>
-      <c r="E176" t="s">
-        <v>11</v>
-      </c>
-      <c r="F176" t="s">
-        <v>16</v>
-      </c>
-      <c r="G176" t="s">
-        <v>536</v>
       </c>
       <c r="H176">
         <v>0.16669999999999999</v>
@@ -8344,11 +8372,11 @@
       <c r="B177" s="3">
         <v>45762</v>
       </c>
-      <c r="C177" t="s">
-        <v>537</v>
-      </c>
-      <c r="D177" t="s">
-        <v>538</v>
+      <c r="C177" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="D177" s="4" t="s">
+        <v>536</v>
       </c>
       <c r="E177" t="s">
         <v>11</v>
@@ -8357,7 +8385,7 @@
         <v>12</v>
       </c>
       <c r="G177" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="H177">
         <v>0.16669999999999999</v>
@@ -8373,20 +8401,20 @@
       <c r="B178" s="3">
         <v>45762</v>
       </c>
-      <c r="C178" t="s">
+      <c r="C178" s="4" t="s">
+        <v>538</v>
+      </c>
+      <c r="D178" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="E178" t="s">
+        <v>11</v>
+      </c>
+      <c r="F178" t="s">
+        <v>16</v>
+      </c>
+      <c r="G178" t="s">
         <v>540</v>
-      </c>
-      <c r="D178" t="s">
-        <v>541</v>
-      </c>
-      <c r="E178" t="s">
-        <v>11</v>
-      </c>
-      <c r="F178" t="s">
-        <v>16</v>
-      </c>
-      <c r="G178" t="s">
-        <v>542</v>
       </c>
       <c r="H178">
         <v>0.16669999999999999</v>
@@ -8402,20 +8430,20 @@
       <c r="B179" s="3">
         <v>45762</v>
       </c>
-      <c r="C179" t="s">
+      <c r="C179" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="D179" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E179" t="s">
+        <v>11</v>
+      </c>
+      <c r="F179" t="s">
+        <v>16</v>
+      </c>
+      <c r="G179" t="s">
         <v>543</v>
-      </c>
-      <c r="D179" t="s">
-        <v>544</v>
-      </c>
-      <c r="E179" t="s">
-        <v>11</v>
-      </c>
-      <c r="F179" t="s">
-        <v>16</v>
-      </c>
-      <c r="G179" t="s">
-        <v>545</v>
       </c>
       <c r="H179">
         <v>0.16669999999999999</v>
@@ -8431,20 +8459,20 @@
       <c r="B180" s="3">
         <v>45762</v>
       </c>
-      <c r="C180" t="s">
+      <c r="C180" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="D180" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="E180" t="s">
+        <v>11</v>
+      </c>
+      <c r="F180" t="s">
+        <v>16</v>
+      </c>
+      <c r="G180" t="s">
         <v>546</v>
-      </c>
-      <c r="D180" t="s">
-        <v>547</v>
-      </c>
-      <c r="E180" t="s">
-        <v>11</v>
-      </c>
-      <c r="F180" t="s">
-        <v>16</v>
-      </c>
-      <c r="G180" t="s">
-        <v>548</v>
       </c>
       <c r="H180">
         <v>0.16669999999999999</v>
@@ -8460,11 +8488,11 @@
       <c r="B181" s="3">
         <v>45762</v>
       </c>
-      <c r="C181" t="s">
-        <v>549</v>
-      </c>
-      <c r="D181" t="s">
-        <v>550</v>
+      <c r="C181" s="4" t="s">
+        <v>547</v>
+      </c>
+      <c r="D181" s="4" t="s">
+        <v>548</v>
       </c>
       <c r="E181" t="s">
         <v>11</v>
@@ -8473,7 +8501,7 @@
         <v>12</v>
       </c>
       <c r="G181" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="H181">
         <v>0.16669999999999999</v>
@@ -8489,20 +8517,20 @@
       <c r="B182" s="3">
         <v>45762</v>
       </c>
-      <c r="C182" t="s">
+      <c r="C182" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="D182" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="E182" t="s">
+        <v>11</v>
+      </c>
+      <c r="F182" t="s">
+        <v>16</v>
+      </c>
+      <c r="G182" t="s">
         <v>552</v>
-      </c>
-      <c r="D182" t="s">
-        <v>553</v>
-      </c>
-      <c r="E182" t="s">
-        <v>11</v>
-      </c>
-      <c r="F182" t="s">
-        <v>16</v>
-      </c>
-      <c r="G182" t="s">
-        <v>554</v>
       </c>
       <c r="H182">
         <v>0.16669999999999999</v>
@@ -8518,20 +8546,20 @@
       <c r="B183" s="3">
         <v>45762</v>
       </c>
-      <c r="C183" t="s">
+      <c r="C183" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="D183" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="E183" t="s">
+        <v>11</v>
+      </c>
+      <c r="F183" t="s">
+        <v>16</v>
+      </c>
+      <c r="G183" t="s">
         <v>555</v>
-      </c>
-      <c r="D183" t="s">
-        <v>556</v>
-      </c>
-      <c r="E183" t="s">
-        <v>11</v>
-      </c>
-      <c r="F183" t="s">
-        <v>16</v>
-      </c>
-      <c r="G183" t="s">
-        <v>557</v>
       </c>
       <c r="H183">
         <v>0.16669999999999999</v>
@@ -8547,20 +8575,20 @@
       <c r="B184" s="3">
         <v>45762</v>
       </c>
-      <c r="C184" t="s">
+      <c r="C184" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="D184" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="E184" t="s">
+        <v>11</v>
+      </c>
+      <c r="F184" t="s">
+        <v>16</v>
+      </c>
+      <c r="G184" t="s">
         <v>558</v>
-      </c>
-      <c r="D184" t="s">
-        <v>559</v>
-      </c>
-      <c r="E184" t="s">
-        <v>11</v>
-      </c>
-      <c r="F184" t="s">
-        <v>16</v>
-      </c>
-      <c r="G184" t="s">
-        <v>560</v>
       </c>
       <c r="H184">
         <v>0.16669999999999999</v>
@@ -8576,20 +8604,20 @@
       <c r="B185" s="3">
         <v>45762</v>
       </c>
-      <c r="C185" t="s">
+      <c r="C185" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="D185" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="E185" t="s">
+        <v>11</v>
+      </c>
+      <c r="F185" t="s">
+        <v>16</v>
+      </c>
+      <c r="G185" t="s">
         <v>561</v>
-      </c>
-      <c r="D185" t="s">
-        <v>562</v>
-      </c>
-      <c r="E185" t="s">
-        <v>11</v>
-      </c>
-      <c r="F185" t="s">
-        <v>16</v>
-      </c>
-      <c r="G185" t="s">
-        <v>563</v>
       </c>
       <c r="H185">
         <v>0.16669999999999999</v>
@@ -8605,11 +8633,11 @@
       <c r="B186" s="3">
         <v>45762</v>
       </c>
-      <c r="C186" t="s">
-        <v>564</v>
-      </c>
-      <c r="D186" t="s">
-        <v>565</v>
+      <c r="C186" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="D186" s="4" t="s">
+        <v>563</v>
       </c>
       <c r="E186" t="s">
         <v>11</v>
@@ -8618,7 +8646,7 @@
         <v>12</v>
       </c>
       <c r="G186" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H186">
         <v>0.16669999999999999</v>
@@ -8634,20 +8662,20 @@
       <c r="B187" s="3">
         <v>45762</v>
       </c>
-      <c r="C187" t="s">
+      <c r="C187" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="D187" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="E187" t="s">
+        <v>11</v>
+      </c>
+      <c r="F187" t="s">
+        <v>16</v>
+      </c>
+      <c r="G187" t="s">
         <v>567</v>
-      </c>
-      <c r="D187" t="s">
-        <v>568</v>
-      </c>
-      <c r="E187" t="s">
-        <v>11</v>
-      </c>
-      <c r="F187" t="s">
-        <v>16</v>
-      </c>
-      <c r="G187" t="s">
-        <v>569</v>
       </c>
       <c r="H187">
         <v>0.16669999999999999</v>
@@ -8663,20 +8691,20 @@
       <c r="B188" s="3">
         <v>45762</v>
       </c>
-      <c r="C188" t="s">
+      <c r="C188" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="D188" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="E188" t="s">
+        <v>11</v>
+      </c>
+      <c r="F188" t="s">
+        <v>16</v>
+      </c>
+      <c r="G188" t="s">
         <v>570</v>
-      </c>
-      <c r="D188" t="s">
-        <v>571</v>
-      </c>
-      <c r="E188" t="s">
-        <v>11</v>
-      </c>
-      <c r="F188" t="s">
-        <v>16</v>
-      </c>
-      <c r="G188" t="s">
-        <v>572</v>
       </c>
       <c r="H188">
         <v>0.16669999999999999</v>
@@ -8692,20 +8720,20 @@
       <c r="B189" s="3">
         <v>45762</v>
       </c>
-      <c r="C189" t="s">
+      <c r="C189" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="D189" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="E189" t="s">
+        <v>11</v>
+      </c>
+      <c r="F189" t="s">
+        <v>16</v>
+      </c>
+      <c r="G189" t="s">
         <v>573</v>
-      </c>
-      <c r="D189" t="s">
-        <v>574</v>
-      </c>
-      <c r="E189" t="s">
-        <v>11</v>
-      </c>
-      <c r="F189" t="s">
-        <v>16</v>
-      </c>
-      <c r="G189" t="s">
-        <v>575</v>
       </c>
       <c r="H189">
         <v>0.16669999999999999</v>
@@ -8721,11 +8749,11 @@
       <c r="B190" s="3">
         <v>45762</v>
       </c>
-      <c r="C190" t="s">
-        <v>576</v>
-      </c>
-      <c r="D190" t="s">
-        <v>577</v>
+      <c r="C190" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="D190" s="4" t="s">
+        <v>575</v>
       </c>
       <c r="E190" t="s">
         <v>11</v>
@@ -8734,7 +8762,7 @@
         <v>12</v>
       </c>
       <c r="G190" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H190">
         <v>0.16669999999999999</v>
@@ -8750,20 +8778,20 @@
       <c r="B191" s="3">
         <v>45762</v>
       </c>
-      <c r="C191" t="s">
+      <c r="C191" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="D191" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="E191" t="s">
+        <v>11</v>
+      </c>
+      <c r="F191" t="s">
+        <v>16</v>
+      </c>
+      <c r="G191" t="s">
         <v>579</v>
-      </c>
-      <c r="D191" t="s">
-        <v>580</v>
-      </c>
-      <c r="E191" t="s">
-        <v>11</v>
-      </c>
-      <c r="F191" t="s">
-        <v>16</v>
-      </c>
-      <c r="G191" t="s">
-        <v>581</v>
       </c>
       <c r="H191">
         <v>0.16669999999999999</v>
@@ -8779,11 +8807,11 @@
       <c r="B192" s="3">
         <v>45762</v>
       </c>
-      <c r="C192" t="s">
-        <v>582</v>
-      </c>
-      <c r="D192" t="s">
-        <v>583</v>
+      <c r="C192" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="D192" s="4" t="s">
+        <v>581</v>
       </c>
       <c r="E192" t="s">
         <v>11</v>
@@ -8792,7 +8820,7 @@
         <v>12</v>
       </c>
       <c r="G192" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="H192">
         <v>0.16669999999999999</v>
@@ -8808,11 +8836,11 @@
       <c r="B193" s="3">
         <v>45762</v>
       </c>
-      <c r="C193" t="s">
-        <v>585</v>
-      </c>
-      <c r="D193" t="s">
-        <v>586</v>
+      <c r="C193" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="D193" s="4" t="s">
+        <v>584</v>
       </c>
       <c r="E193" t="s">
         <v>11</v>
@@ -8821,7 +8849,7 @@
         <v>12</v>
       </c>
       <c r="G193" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="H193">
         <v>0.16669999999999999</v>
@@ -8837,11 +8865,11 @@
       <c r="B194" s="3">
         <v>45762</v>
       </c>
-      <c r="C194" t="s">
-        <v>588</v>
-      </c>
-      <c r="D194" t="s">
-        <v>589</v>
+      <c r="C194" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="D194" s="4" t="s">
+        <v>587</v>
       </c>
       <c r="E194" t="s">
         <v>11</v>
@@ -8850,7 +8878,7 @@
         <v>12</v>
       </c>
       <c r="G194" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="H194">
         <v>0.16669999999999999</v>
@@ -8866,11 +8894,11 @@
       <c r="B195" s="3">
         <v>45762</v>
       </c>
-      <c r="C195" t="s">
-        <v>591</v>
-      </c>
-      <c r="D195" t="s">
-        <v>592</v>
+      <c r="C195" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="D195" s="4" t="s">
+        <v>590</v>
       </c>
       <c r="E195" t="s">
         <v>11</v>
@@ -8879,7 +8907,7 @@
         <v>12</v>
       </c>
       <c r="G195" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="H195">
         <v>0.16669999999999999</v>
@@ -8895,20 +8923,20 @@
       <c r="B196" s="3">
         <v>45762</v>
       </c>
-      <c r="C196" t="s">
+      <c r="C196" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="D196" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="E196" t="s">
+        <v>11</v>
+      </c>
+      <c r="F196" t="s">
+        <v>16</v>
+      </c>
+      <c r="G196" t="s">
         <v>594</v>
-      </c>
-      <c r="D196" t="s">
-        <v>595</v>
-      </c>
-      <c r="E196" t="s">
-        <v>11</v>
-      </c>
-      <c r="F196" t="s">
-        <v>16</v>
-      </c>
-      <c r="G196" t="s">
-        <v>596</v>
       </c>
       <c r="H196">
         <v>0.16669999999999999</v>
@@ -8924,20 +8952,20 @@
       <c r="B197" s="3">
         <v>45762</v>
       </c>
-      <c r="C197" t="s">
+      <c r="C197" s="4" t="s">
+        <v>595</v>
+      </c>
+      <c r="D197" s="4" t="s">
+        <v>596</v>
+      </c>
+      <c r="E197" t="s">
+        <v>11</v>
+      </c>
+      <c r="F197" t="s">
+        <v>16</v>
+      </c>
+      <c r="G197" t="s">
         <v>597</v>
-      </c>
-      <c r="D197" t="s">
-        <v>598</v>
-      </c>
-      <c r="E197" t="s">
-        <v>11</v>
-      </c>
-      <c r="F197" t="s">
-        <v>16</v>
-      </c>
-      <c r="G197" t="s">
-        <v>599</v>
       </c>
       <c r="H197">
         <v>0.16669999999999999</v>
@@ -8953,20 +8981,20 @@
       <c r="B198" s="3">
         <v>45762</v>
       </c>
-      <c r="C198" t="s">
+      <c r="C198" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="D198" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="E198" t="s">
+        <v>11</v>
+      </c>
+      <c r="F198" t="s">
+        <v>16</v>
+      </c>
+      <c r="G198" t="s">
         <v>600</v>
-      </c>
-      <c r="D198" t="s">
-        <v>601</v>
-      </c>
-      <c r="E198" t="s">
-        <v>11</v>
-      </c>
-      <c r="F198" t="s">
-        <v>16</v>
-      </c>
-      <c r="G198" t="s">
-        <v>602</v>
       </c>
       <c r="H198">
         <v>0.16669999999999999</v>
@@ -8982,20 +9010,20 @@
       <c r="B199" s="3">
         <v>45762</v>
       </c>
-      <c r="C199" t="s">
+      <c r="C199" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="D199" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="E199" t="s">
+        <v>11</v>
+      </c>
+      <c r="F199" t="s">
+        <v>16</v>
+      </c>
+      <c r="G199" t="s">
         <v>603</v>
-      </c>
-      <c r="D199" t="s">
-        <v>604</v>
-      </c>
-      <c r="E199" t="s">
-        <v>11</v>
-      </c>
-      <c r="F199" t="s">
-        <v>16</v>
-      </c>
-      <c r="G199" t="s">
-        <v>605</v>
       </c>
       <c r="H199">
         <v>0.16669999999999999</v>
@@ -9011,20 +9039,20 @@
       <c r="B200" s="3">
         <v>45762</v>
       </c>
-      <c r="C200" t="s">
+      <c r="C200" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="D200" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="E200" t="s">
+        <v>11</v>
+      </c>
+      <c r="F200" t="s">
+        <v>16</v>
+      </c>
+      <c r="G200" t="s">
         <v>606</v>
-      </c>
-      <c r="D200" t="s">
-        <v>607</v>
-      </c>
-      <c r="E200" t="s">
-        <v>11</v>
-      </c>
-      <c r="F200" t="s">
-        <v>16</v>
-      </c>
-      <c r="G200" t="s">
-        <v>608</v>
       </c>
       <c r="H200">
         <v>0.16669999999999999</v>
@@ -9040,11 +9068,11 @@
       <c r="B201" s="3">
         <v>45762</v>
       </c>
-      <c r="C201" t="s">
-        <v>609</v>
-      </c>
-      <c r="D201" t="s">
-        <v>610</v>
+      <c r="C201" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="D201" s="4" t="s">
+        <v>608</v>
       </c>
       <c r="E201" t="s">
         <v>11</v>
@@ -9053,7 +9081,7 @@
         <v>12</v>
       </c>
       <c r="G201" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="H201">
         <v>0.16669999999999999</v>
@@ -9069,11 +9097,11 @@
       <c r="B202" s="3">
         <v>45762</v>
       </c>
-      <c r="C202" t="s">
-        <v>612</v>
-      </c>
-      <c r="D202" t="s">
-        <v>613</v>
+      <c r="C202" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="D202" s="4" t="s">
+        <v>611</v>
       </c>
       <c r="E202" t="s">
         <v>11</v>
@@ -9082,7 +9110,7 @@
         <v>12</v>
       </c>
       <c r="G202" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="H202">
         <v>0.16669999999999999</v>
@@ -9098,11 +9126,11 @@
       <c r="B203" s="3">
         <v>45762</v>
       </c>
-      <c r="C203" t="s">
-        <v>615</v>
-      </c>
-      <c r="D203" t="s">
-        <v>616</v>
+      <c r="C203" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="D203" s="4" t="s">
+        <v>945</v>
       </c>
       <c r="E203" t="s">
         <v>11</v>
@@ -9111,7 +9139,7 @@
         <v>12</v>
       </c>
       <c r="G203" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="H203">
         <v>0.16669999999999999</v>
@@ -9127,11 +9155,11 @@
       <c r="B204" s="3">
         <v>45762</v>
       </c>
-      <c r="C204" t="s">
-        <v>618</v>
-      </c>
-      <c r="D204" t="s">
-        <v>619</v>
+      <c r="C204" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="D204" s="4" t="s">
+        <v>616</v>
       </c>
       <c r="E204" t="s">
         <v>11</v>
@@ -9140,7 +9168,7 @@
         <v>16</v>
       </c>
       <c r="G204" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="H204">
         <v>0.16669999999999999</v>
@@ -9156,11 +9184,11 @@
       <c r="B205" s="3">
         <v>45762</v>
       </c>
-      <c r="C205" t="s">
-        <v>621</v>
-      </c>
-      <c r="D205" t="s">
-        <v>622</v>
+      <c r="C205" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="D205" s="4" t="s">
+        <v>619</v>
       </c>
       <c r="E205" t="s">
         <v>11</v>
@@ -9169,7 +9197,7 @@
         <v>12</v>
       </c>
       <c r="G205" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="H205">
         <v>0.16669999999999999</v>
@@ -9185,11 +9213,11 @@
       <c r="B206" s="3">
         <v>45762</v>
       </c>
-      <c r="C206" t="s">
-        <v>624</v>
-      </c>
-      <c r="D206" t="s">
-        <v>625</v>
+      <c r="C206" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="D206" s="4" t="s">
+        <v>622</v>
       </c>
       <c r="E206" t="s">
         <v>11</v>
@@ -9198,7 +9226,7 @@
         <v>12</v>
       </c>
       <c r="G206" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="H206">
         <v>0.16669999999999999</v>
@@ -9214,11 +9242,11 @@
       <c r="B207" s="3">
         <v>45762</v>
       </c>
-      <c r="C207" t="s">
-        <v>627</v>
-      </c>
-      <c r="D207" t="s">
-        <v>628</v>
+      <c r="C207" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="D207" s="4" t="s">
+        <v>625</v>
       </c>
       <c r="E207" t="s">
         <v>11</v>
@@ -9227,7 +9255,7 @@
         <v>16</v>
       </c>
       <c r="G207" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="H207">
         <v>0.16669999999999999</v>
@@ -9243,11 +9271,11 @@
       <c r="B208" s="3">
         <v>45762</v>
       </c>
-      <c r="C208" t="s">
-        <v>630</v>
-      </c>
-      <c r="D208" t="s">
-        <v>631</v>
+      <c r="C208" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="D208" s="4" t="s">
+        <v>628</v>
       </c>
       <c r="E208" t="s">
         <v>11</v>
@@ -9256,7 +9284,7 @@
         <v>12</v>
       </c>
       <c r="G208" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="H208">
         <v>0.16669999999999999</v>
@@ -9272,11 +9300,11 @@
       <c r="B209" s="3">
         <v>45762</v>
       </c>
-      <c r="C209" t="s">
-        <v>633</v>
-      </c>
-      <c r="D209" t="s">
-        <v>634</v>
+      <c r="C209" s="4" t="s">
+        <v>630</v>
+      </c>
+      <c r="D209" s="4" t="s">
+        <v>631</v>
       </c>
       <c r="E209" t="s">
         <v>11</v>
@@ -9285,7 +9313,7 @@
         <v>16</v>
       </c>
       <c r="G209" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="H209">
         <v>0.16669999999999999</v>
@@ -9301,11 +9329,11 @@
       <c r="B210" s="3">
         <v>45762</v>
       </c>
-      <c r="C210" t="s">
-        <v>636</v>
-      </c>
-      <c r="D210" t="s">
-        <v>637</v>
+      <c r="C210" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="D210" s="4" t="s">
+        <v>634</v>
       </c>
       <c r="E210" t="s">
         <v>11</v>
@@ -9314,7 +9342,7 @@
         <v>16</v>
       </c>
       <c r="G210" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="H210">
         <v>0.16669999999999999</v>
@@ -9330,11 +9358,11 @@
       <c r="B211" s="3">
         <v>45762</v>
       </c>
-      <c r="C211" t="s">
-        <v>639</v>
-      </c>
-      <c r="D211" t="s">
-        <v>640</v>
+      <c r="C211" s="4" t="s">
+        <v>636</v>
+      </c>
+      <c r="D211" s="4" t="s">
+        <v>637</v>
       </c>
       <c r="E211" t="s">
         <v>11</v>
@@ -9343,7 +9371,7 @@
         <v>16</v>
       </c>
       <c r="G211" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="H211">
         <v>0.16669999999999999</v>
@@ -9359,11 +9387,11 @@
       <c r="B212" s="3">
         <v>45762</v>
       </c>
-      <c r="C212" t="s">
-        <v>642</v>
-      </c>
-      <c r="D212" t="s">
-        <v>643</v>
+      <c r="C212" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="D212" s="4" t="s">
+        <v>640</v>
       </c>
       <c r="E212" t="s">
         <v>11</v>
@@ -9372,7 +9400,7 @@
         <v>12</v>
       </c>
       <c r="G212" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="H212">
         <v>0.16669999999999999</v>
@@ -9388,11 +9416,11 @@
       <c r="B213" s="3">
         <v>45762</v>
       </c>
-      <c r="C213" t="s">
-        <v>645</v>
-      </c>
-      <c r="D213" t="s">
-        <v>646</v>
+      <c r="C213" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="D213" s="4" t="s">
+        <v>643</v>
       </c>
       <c r="E213" t="s">
         <v>11</v>
@@ -9401,7 +9429,7 @@
         <v>12</v>
       </c>
       <c r="G213" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="H213">
         <v>0.16669999999999999</v>
@@ -9417,11 +9445,11 @@
       <c r="B214" s="3">
         <v>45762</v>
       </c>
-      <c r="C214" t="s">
-        <v>648</v>
-      </c>
-      <c r="D214" t="s">
-        <v>649</v>
+      <c r="C214" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="D214" s="4" t="s">
+        <v>646</v>
       </c>
       <c r="E214" t="s">
         <v>11</v>
@@ -9430,7 +9458,7 @@
         <v>16</v>
       </c>
       <c r="G214" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="H214">
         <v>0.16669999999999999</v>
@@ -9446,11 +9474,11 @@
       <c r="B215" s="3">
         <v>45762</v>
       </c>
-      <c r="C215" t="s">
-        <v>651</v>
-      </c>
-      <c r="D215" t="s">
-        <v>652</v>
+      <c r="C215" s="4" t="s">
+        <v>648</v>
+      </c>
+      <c r="D215" s="4" t="s">
+        <v>649</v>
       </c>
       <c r="E215" t="s">
         <v>11</v>
@@ -9459,7 +9487,7 @@
         <v>16</v>
       </c>
       <c r="G215" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="H215">
         <v>0.16669999999999999</v>
@@ -9475,11 +9503,11 @@
       <c r="B216" s="3">
         <v>45762</v>
       </c>
-      <c r="C216" t="s">
-        <v>654</v>
-      </c>
-      <c r="D216" t="s">
-        <v>655</v>
+      <c r="C216" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="D216" s="4" t="s">
+        <v>652</v>
       </c>
       <c r="E216" t="s">
         <v>11</v>
@@ -9488,7 +9516,7 @@
         <v>16</v>
       </c>
       <c r="G216" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="H216">
         <v>0.16669999999999999</v>
@@ -9504,11 +9532,11 @@
       <c r="B217" s="3">
         <v>45762</v>
       </c>
-      <c r="C217" t="s">
-        <v>657</v>
-      </c>
-      <c r="D217" t="s">
-        <v>658</v>
+      <c r="C217" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D217" s="4" t="s">
+        <v>655</v>
       </c>
       <c r="E217" t="s">
         <v>11</v>
@@ -9517,7 +9545,7 @@
         <v>16</v>
       </c>
       <c r="G217" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="H217">
         <v>0.16669999999999999</v>
@@ -9533,11 +9561,11 @@
       <c r="B218" s="3">
         <v>45762</v>
       </c>
-      <c r="C218" t="s">
-        <v>660</v>
-      </c>
-      <c r="D218" t="s">
-        <v>661</v>
+      <c r="C218" s="4" t="s">
+        <v>657</v>
+      </c>
+      <c r="D218" s="4" t="s">
+        <v>658</v>
       </c>
       <c r="E218" t="s">
         <v>11</v>
@@ -9546,7 +9574,7 @@
         <v>16</v>
       </c>
       <c r="G218" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="H218">
         <v>0.16669999999999999</v>
@@ -9562,11 +9590,11 @@
       <c r="B219" s="3">
         <v>45762</v>
       </c>
-      <c r="C219" t="s">
-        <v>663</v>
-      </c>
-      <c r="D219" t="s">
-        <v>664</v>
+      <c r="C219" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="D219" s="4" t="s">
+        <v>661</v>
       </c>
       <c r="E219" t="s">
         <v>11</v>
@@ -9575,7 +9603,7 @@
         <v>16</v>
       </c>
       <c r="G219" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="H219">
         <v>0.16669999999999999</v>
@@ -9591,11 +9619,11 @@
       <c r="B220" s="3">
         <v>45762</v>
       </c>
-      <c r="C220" t="s">
-        <v>666</v>
-      </c>
-      <c r="D220" t="s">
-        <v>667</v>
+      <c r="C220" s="4" t="s">
+        <v>663</v>
+      </c>
+      <c r="D220" s="4" t="s">
+        <v>664</v>
       </c>
       <c r="E220" t="s">
         <v>11</v>
@@ -9604,7 +9632,7 @@
         <v>16</v>
       </c>
       <c r="G220" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="H220">
         <v>0.16669999999999999</v>
@@ -9620,11 +9648,11 @@
       <c r="B221" s="3">
         <v>45762</v>
       </c>
-      <c r="C221" t="s">
-        <v>669</v>
-      </c>
-      <c r="D221" t="s">
-        <v>670</v>
+      <c r="C221" s="4" t="s">
+        <v>666</v>
+      </c>
+      <c r="D221" s="4" t="s">
+        <v>667</v>
       </c>
       <c r="E221" t="s">
         <v>11</v>
@@ -9633,7 +9661,7 @@
         <v>16</v>
       </c>
       <c r="G221" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="H221">
         <v>0.16669999999999999</v>
@@ -9649,11 +9677,11 @@
       <c r="B222" s="3">
         <v>45762</v>
       </c>
-      <c r="C222" t="s">
-        <v>672</v>
-      </c>
-      <c r="D222" t="s">
-        <v>673</v>
+      <c r="C222" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="D222" s="4" t="s">
+        <v>946</v>
       </c>
       <c r="E222" t="s">
         <v>11</v>
@@ -9662,7 +9690,7 @@
         <v>16</v>
       </c>
       <c r="G222" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="H222">
         <v>0.16669999999999999</v>
@@ -9678,11 +9706,11 @@
       <c r="B223" s="3">
         <v>45762</v>
       </c>
-      <c r="C223" t="s">
-        <v>675</v>
-      </c>
-      <c r="D223" t="s">
-        <v>676</v>
+      <c r="C223" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="D223" s="4" t="s">
+        <v>672</v>
       </c>
       <c r="E223" t="s">
         <v>11</v>
@@ -9691,7 +9719,7 @@
         <v>12</v>
       </c>
       <c r="G223" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="H223">
         <v>0.16669999999999999</v>
@@ -9707,11 +9735,11 @@
       <c r="B224" s="3">
         <v>45762</v>
       </c>
-      <c r="C224" t="s">
-        <v>678</v>
-      </c>
-      <c r="D224" t="s">
-        <v>679</v>
+      <c r="C224" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="D224" s="4" t="s">
+        <v>675</v>
       </c>
       <c r="E224" t="s">
         <v>11</v>
@@ -9720,7 +9748,7 @@
         <v>12</v>
       </c>
       <c r="G224" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="H224">
         <v>0.16669999999999999</v>
@@ -9736,11 +9764,11 @@
       <c r="B225" s="3">
         <v>45762</v>
       </c>
-      <c r="C225" t="s">
-        <v>681</v>
-      </c>
-      <c r="D225" t="s">
-        <v>682</v>
+      <c r="C225" s="4" t="s">
+        <v>677</v>
+      </c>
+      <c r="D225" s="4" t="s">
+        <v>678</v>
       </c>
       <c r="E225" t="s">
         <v>11</v>
@@ -9749,7 +9777,7 @@
         <v>12</v>
       </c>
       <c r="G225" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="H225">
         <v>0.16669999999999999</v>
@@ -9765,11 +9793,11 @@
       <c r="B226" s="3">
         <v>45762</v>
       </c>
-      <c r="C226" t="s">
-        <v>684</v>
-      </c>
-      <c r="D226" t="s">
-        <v>685</v>
+      <c r="C226" s="4" t="s">
+        <v>680</v>
+      </c>
+      <c r="D226" s="4" t="s">
+        <v>681</v>
       </c>
       <c r="E226" t="s">
         <v>11</v>
@@ -9778,7 +9806,7 @@
         <v>16</v>
       </c>
       <c r="G226" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="H226">
         <v>0.16669999999999999</v>
@@ -9794,11 +9822,11 @@
       <c r="B227" s="3">
         <v>45762</v>
       </c>
-      <c r="C227" t="s">
-        <v>687</v>
-      </c>
-      <c r="D227" t="s">
-        <v>688</v>
+      <c r="C227" s="4" t="s">
+        <v>683</v>
+      </c>
+      <c r="D227" s="4" t="s">
+        <v>684</v>
       </c>
       <c r="E227" t="s">
         <v>11</v>
@@ -9807,7 +9835,7 @@
         <v>12</v>
       </c>
       <c r="G227" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="H227">
         <v>0.16669999999999999</v>
@@ -9823,11 +9851,11 @@
       <c r="B228" s="3">
         <v>45762</v>
       </c>
-      <c r="C228" t="s">
-        <v>690</v>
-      </c>
-      <c r="D228" t="s">
-        <v>691</v>
+      <c r="C228" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="D228" s="4" t="s">
+        <v>687</v>
       </c>
       <c r="E228" t="s">
         <v>11</v>
@@ -9836,7 +9864,7 @@
         <v>16</v>
       </c>
       <c r="G228" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="H228">
         <v>0.16669999999999999</v>
@@ -9852,11 +9880,11 @@
       <c r="B229" s="3">
         <v>45762</v>
       </c>
-      <c r="C229" t="s">
-        <v>693</v>
-      </c>
-      <c r="D229" t="s">
-        <v>694</v>
+      <c r="C229" s="4" t="s">
+        <v>689</v>
+      </c>
+      <c r="D229" s="4" t="s">
+        <v>690</v>
       </c>
       <c r="E229" t="s">
         <v>11</v>
@@ -9865,7 +9893,7 @@
         <v>12</v>
       </c>
       <c r="G229" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="H229">
         <v>0.16669999999999999</v>
@@ -9881,11 +9909,11 @@
       <c r="B230" s="3">
         <v>45762</v>
       </c>
-      <c r="C230" t="s">
-        <v>696</v>
-      </c>
-      <c r="D230" t="s">
-        <v>697</v>
+      <c r="C230" s="4" t="s">
+        <v>692</v>
+      </c>
+      <c r="D230" s="4" t="s">
+        <v>693</v>
       </c>
       <c r="E230" t="s">
         <v>11</v>
@@ -9894,7 +9922,7 @@
         <v>12</v>
       </c>
       <c r="G230" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="H230">
         <v>0.16669999999999999</v>
@@ -9910,11 +9938,11 @@
       <c r="B231" s="3">
         <v>45762</v>
       </c>
-      <c r="C231" t="s">
-        <v>699</v>
-      </c>
-      <c r="D231" t="s">
-        <v>700</v>
+      <c r="C231" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="D231" s="4" t="s">
+        <v>696</v>
       </c>
       <c r="E231" t="s">
         <v>11</v>
@@ -9923,7 +9951,7 @@
         <v>12</v>
       </c>
       <c r="G231" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="H231">
         <v>0.16669999999999999</v>
@@ -9939,11 +9967,11 @@
       <c r="B232" s="3">
         <v>45762</v>
       </c>
-      <c r="C232" t="s">
-        <v>702</v>
-      </c>
-      <c r="D232" t="s">
-        <v>703</v>
+      <c r="C232" s="4" t="s">
+        <v>698</v>
+      </c>
+      <c r="D232" s="4" t="s">
+        <v>699</v>
       </c>
       <c r="E232" t="s">
         <v>11</v>
@@ -9952,7 +9980,7 @@
         <v>12</v>
       </c>
       <c r="G232" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="H232">
         <v>0.16669999999999999</v>
@@ -9968,11 +9996,11 @@
       <c r="B233" s="3">
         <v>45762</v>
       </c>
-      <c r="C233" t="s">
-        <v>705</v>
-      </c>
-      <c r="D233" t="s">
-        <v>706</v>
+      <c r="C233" s="4" t="s">
+        <v>701</v>
+      </c>
+      <c r="D233" s="4" t="s">
+        <v>702</v>
       </c>
       <c r="E233" t="s">
         <v>11</v>
@@ -9981,7 +10009,7 @@
         <v>16</v>
       </c>
       <c r="G233" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="H233">
         <v>0.16669999999999999</v>
@@ -9997,11 +10025,11 @@
       <c r="B234" s="3">
         <v>45762</v>
       </c>
-      <c r="C234" t="s">
-        <v>708</v>
-      </c>
-      <c r="D234" t="s">
-        <v>709</v>
+      <c r="C234" s="4" t="s">
+        <v>704</v>
+      </c>
+      <c r="D234" s="4" t="s">
+        <v>705</v>
       </c>
       <c r="E234" t="s">
         <v>11</v>
@@ -10010,7 +10038,7 @@
         <v>12</v>
       </c>
       <c r="G234" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="H234">
         <v>0.16669999999999999</v>
@@ -10026,11 +10054,11 @@
       <c r="B235" s="3">
         <v>45762</v>
       </c>
-      <c r="C235" t="s">
-        <v>711</v>
-      </c>
-      <c r="D235" t="s">
-        <v>712</v>
+      <c r="C235" s="4" t="s">
+        <v>707</v>
+      </c>
+      <c r="D235" s="4" t="s">
+        <v>708</v>
       </c>
       <c r="E235" t="s">
         <v>11</v>
@@ -10039,7 +10067,7 @@
         <v>16</v>
       </c>
       <c r="G235" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="H235">
         <v>0.16669999999999999</v>
@@ -10055,11 +10083,11 @@
       <c r="B236" s="3">
         <v>45762</v>
       </c>
-      <c r="C236" t="s">
-        <v>714</v>
-      </c>
-      <c r="D236" t="s">
-        <v>715</v>
+      <c r="C236" s="4" t="s">
+        <v>710</v>
+      </c>
+      <c r="D236" s="4" t="s">
+        <v>711</v>
       </c>
       <c r="E236" t="s">
         <v>11</v>
@@ -10068,7 +10096,7 @@
         <v>16</v>
       </c>
       <c r="G236" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="H236">
         <v>0.16669999999999999</v>
@@ -10084,11 +10112,11 @@
       <c r="B237" s="3">
         <v>45762</v>
       </c>
-      <c r="C237" t="s">
-        <v>717</v>
-      </c>
-      <c r="D237" t="s">
-        <v>718</v>
+      <c r="C237" s="4" t="s">
+        <v>713</v>
+      </c>
+      <c r="D237" s="4" t="s">
+        <v>714</v>
       </c>
       <c r="E237" t="s">
         <v>11</v>
@@ -10097,7 +10125,7 @@
         <v>12</v>
       </c>
       <c r="G237" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="H237">
         <v>0.16669999999999999</v>
@@ -10113,11 +10141,11 @@
       <c r="B238" s="3">
         <v>45762</v>
       </c>
-      <c r="C238" t="s">
-        <v>720</v>
-      </c>
-      <c r="D238" t="s">
-        <v>721</v>
+      <c r="C238" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D238" s="4" t="s">
+        <v>717</v>
       </c>
       <c r="E238" t="s">
         <v>11</v>
@@ -10126,7 +10154,7 @@
         <v>16</v>
       </c>
       <c r="G238" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="H238">
         <v>0.16669999999999999</v>
@@ -10142,11 +10170,11 @@
       <c r="B239" s="3">
         <v>45762</v>
       </c>
-      <c r="C239" t="s">
-        <v>723</v>
-      </c>
-      <c r="D239" t="s">
-        <v>724</v>
+      <c r="C239" s="4" t="s">
+        <v>719</v>
+      </c>
+      <c r="D239" s="4" t="s">
+        <v>720</v>
       </c>
       <c r="E239" t="s">
         <v>11</v>
@@ -10155,7 +10183,7 @@
         <v>12</v>
       </c>
       <c r="G239" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="H239">
         <v>0.16669999999999999</v>
@@ -10171,11 +10199,11 @@
       <c r="B240" s="3">
         <v>45762</v>
       </c>
-      <c r="C240" t="s">
-        <v>726</v>
-      </c>
-      <c r="D240" t="s">
-        <v>727</v>
+      <c r="C240" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="D240" s="4" t="s">
+        <v>723</v>
       </c>
       <c r="E240" t="s">
         <v>11</v>
@@ -10184,7 +10212,7 @@
         <v>16</v>
       </c>
       <c r="G240" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="H240">
         <v>0.16669999999999999</v>
@@ -10200,11 +10228,11 @@
       <c r="B241" s="3">
         <v>45762</v>
       </c>
-      <c r="C241" t="s">
-        <v>729</v>
-      </c>
-      <c r="D241" t="s">
-        <v>730</v>
+      <c r="C241" s="4" t="s">
+        <v>725</v>
+      </c>
+      <c r="D241" s="4" t="s">
+        <v>726</v>
       </c>
       <c r="E241" t="s">
         <v>11</v>
@@ -10213,7 +10241,7 @@
         <v>16</v>
       </c>
       <c r="G241" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="H241">
         <v>0.16669999999999999</v>
@@ -10229,11 +10257,11 @@
       <c r="B242" s="3">
         <v>45762</v>
       </c>
-      <c r="C242" t="s">
-        <v>732</v>
-      </c>
-      <c r="D242" t="s">
-        <v>733</v>
+      <c r="C242" s="4" t="s">
+        <v>728</v>
+      </c>
+      <c r="D242" s="4" t="s">
+        <v>947</v>
       </c>
       <c r="E242" t="s">
         <v>11</v>
@@ -10242,7 +10270,7 @@
         <v>16</v>
       </c>
       <c r="G242" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="H242">
         <v>0.16669999999999999</v>
@@ -10258,11 +10286,11 @@
       <c r="B243" s="3">
         <v>45762</v>
       </c>
-      <c r="C243" t="s">
-        <v>735</v>
-      </c>
-      <c r="D243" t="s">
-        <v>736</v>
+      <c r="C243" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="D243" s="4" t="s">
+        <v>731</v>
       </c>
       <c r="E243" t="s">
         <v>11</v>
@@ -10271,7 +10299,7 @@
         <v>16</v>
       </c>
       <c r="G243" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
       <c r="H243">
         <v>0.16669999999999999</v>
@@ -10287,11 +10315,11 @@
       <c r="B244" s="3">
         <v>45762</v>
       </c>
-      <c r="C244" t="s">
-        <v>738</v>
-      </c>
-      <c r="D244" t="s">
-        <v>739</v>
+      <c r="C244" s="4" t="s">
+        <v>733</v>
+      </c>
+      <c r="D244" s="4" t="s">
+        <v>734</v>
       </c>
       <c r="E244" t="s">
         <v>11</v>
@@ -10300,7 +10328,7 @@
         <v>16</v>
       </c>
       <c r="G244" t="s">
-        <v>740</v>
+        <v>735</v>
       </c>
       <c r="H244">
         <v>0.16669999999999999</v>
@@ -10316,11 +10344,11 @@
       <c r="B245" s="3">
         <v>45762</v>
       </c>
-      <c r="C245" t="s">
-        <v>741</v>
-      </c>
-      <c r="D245" t="s">
-        <v>742</v>
+      <c r="C245" s="4" t="s">
+        <v>736</v>
+      </c>
+      <c r="D245" s="4" t="s">
+        <v>737</v>
       </c>
       <c r="E245" t="s">
         <v>11</v>
@@ -10329,7 +10357,7 @@
         <v>12</v>
       </c>
       <c r="G245" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="H245">
         <v>0.16669999999999999</v>
@@ -10345,11 +10373,11 @@
       <c r="B246" s="3">
         <v>45762</v>
       </c>
-      <c r="C246" t="s">
-        <v>744</v>
-      </c>
-      <c r="D246" t="s">
-        <v>745</v>
+      <c r="C246" s="4" t="s">
+        <v>739</v>
+      </c>
+      <c r="D246" s="4" t="s">
+        <v>740</v>
       </c>
       <c r="E246" t="s">
         <v>11</v>
@@ -10358,7 +10386,7 @@
         <v>16</v>
       </c>
       <c r="G246" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
       <c r="H246">
         <v>0.16669999999999999</v>
@@ -10374,11 +10402,11 @@
       <c r="B247" s="3">
         <v>45762</v>
       </c>
-      <c r="C247" t="s">
-        <v>747</v>
-      </c>
-      <c r="D247" t="s">
-        <v>748</v>
+      <c r="C247" s="4" t="s">
+        <v>742</v>
+      </c>
+      <c r="D247" s="4" t="s">
+        <v>743</v>
       </c>
       <c r="E247" t="s">
         <v>11</v>
@@ -10387,7 +10415,7 @@
         <v>16</v>
       </c>
       <c r="G247" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="H247">
         <v>0.16669999999999999</v>
@@ -10403,11 +10431,11 @@
       <c r="B248" s="3">
         <v>45762</v>
       </c>
-      <c r="C248" t="s">
-        <v>750</v>
-      </c>
-      <c r="D248" t="s">
-        <v>751</v>
+      <c r="C248" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="D248" s="4" t="s">
+        <v>746</v>
       </c>
       <c r="E248" t="s">
         <v>11</v>
@@ -10416,7 +10444,7 @@
         <v>16</v>
       </c>
       <c r="G248" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="H248">
         <v>0.16669999999999999</v>
@@ -10432,11 +10460,11 @@
       <c r="B249" s="3">
         <v>45762</v>
       </c>
-      <c r="C249" t="s">
-        <v>753</v>
-      </c>
-      <c r="D249" t="s">
-        <v>754</v>
+      <c r="C249" s="4" t="s">
+        <v>748</v>
+      </c>
+      <c r="D249" s="4" t="s">
+        <v>749</v>
       </c>
       <c r="E249" t="s">
         <v>11</v>
@@ -10445,7 +10473,7 @@
         <v>12</v>
       </c>
       <c r="G249" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="H249">
         <v>0.16669999999999999</v>
@@ -10461,11 +10489,11 @@
       <c r="B250" s="3">
         <v>45762</v>
       </c>
-      <c r="C250" t="s">
-        <v>756</v>
-      </c>
-      <c r="D250" t="s">
-        <v>757</v>
+      <c r="C250" s="4" t="s">
+        <v>751</v>
+      </c>
+      <c r="D250" s="4" t="s">
+        <v>752</v>
       </c>
       <c r="E250" t="s">
         <v>11</v>
@@ -10474,7 +10502,7 @@
         <v>16</v>
       </c>
       <c r="G250" t="s">
-        <v>758</v>
+        <v>753</v>
       </c>
       <c r="H250">
         <v>0.16669999999999999</v>
@@ -10490,11 +10518,11 @@
       <c r="B251" s="3">
         <v>45762</v>
       </c>
-      <c r="C251" t="s">
-        <v>759</v>
-      </c>
-      <c r="D251" t="s">
-        <v>760</v>
+      <c r="C251" s="4" t="s">
+        <v>754</v>
+      </c>
+      <c r="D251" s="4" t="s">
+        <v>755</v>
       </c>
       <c r="E251" t="s">
         <v>11</v>
@@ -10503,7 +10531,7 @@
         <v>16</v>
       </c>
       <c r="G251" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="H251">
         <v>0.16669999999999999</v>
@@ -10519,11 +10547,11 @@
       <c r="B252" s="3">
         <v>45762</v>
       </c>
-      <c r="C252" t="s">
-        <v>762</v>
-      </c>
-      <c r="D252" t="s">
-        <v>763</v>
+      <c r="C252" s="4" t="s">
+        <v>757</v>
+      </c>
+      <c r="D252" s="4" t="s">
+        <v>758</v>
       </c>
       <c r="E252" t="s">
         <v>11</v>
@@ -10532,7 +10560,7 @@
         <v>16</v>
       </c>
       <c r="G252" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
       <c r="H252">
         <v>0.16669999999999999</v>
@@ -10548,11 +10576,11 @@
       <c r="B253" s="3">
         <v>45762</v>
       </c>
-      <c r="C253" t="s">
-        <v>765</v>
-      </c>
-      <c r="D253" t="s">
-        <v>766</v>
+      <c r="C253" s="4" t="s">
+        <v>760</v>
+      </c>
+      <c r="D253" s="4" t="s">
+        <v>761</v>
       </c>
       <c r="E253" t="s">
         <v>11</v>
@@ -10561,7 +10589,7 @@
         <v>12</v>
       </c>
       <c r="G253" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="H253">
         <v>0.16669999999999999</v>
@@ -10577,11 +10605,11 @@
       <c r="B254" s="3">
         <v>45762</v>
       </c>
-      <c r="C254" t="s">
-        <v>768</v>
-      </c>
-      <c r="D254" t="s">
-        <v>769</v>
+      <c r="C254" s="4" t="s">
+        <v>763</v>
+      </c>
+      <c r="D254" s="4" t="s">
+        <v>764</v>
       </c>
       <c r="E254" t="s">
         <v>11</v>
@@ -10590,7 +10618,7 @@
         <v>12</v>
       </c>
       <c r="G254" t="s">
-        <v>770</v>
+        <v>765</v>
       </c>
       <c r="H254">
         <v>0.16669999999999999</v>
@@ -10606,11 +10634,11 @@
       <c r="B255" s="3">
         <v>45762</v>
       </c>
-      <c r="C255" t="s">
-        <v>771</v>
-      </c>
-      <c r="D255" t="s">
-        <v>772</v>
+      <c r="C255" s="4" t="s">
+        <v>766</v>
+      </c>
+      <c r="D255" s="4" t="s">
+        <v>767</v>
       </c>
       <c r="E255" t="s">
         <v>11</v>
@@ -10619,7 +10647,7 @@
         <v>16</v>
       </c>
       <c r="G255" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="H255">
         <v>0.16669999999999999</v>
@@ -10635,11 +10663,11 @@
       <c r="B256" s="3">
         <v>45762</v>
       </c>
-      <c r="C256" t="s">
-        <v>774</v>
-      </c>
-      <c r="D256" t="s">
-        <v>775</v>
+      <c r="C256" s="4" t="s">
+        <v>769</v>
+      </c>
+      <c r="D256" s="4" t="s">
+        <v>770</v>
       </c>
       <c r="E256" t="s">
         <v>11</v>
@@ -10648,7 +10676,7 @@
         <v>16</v>
       </c>
       <c r="G256" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="H256">
         <v>0.16669999999999999</v>
@@ -10664,11 +10692,11 @@
       <c r="B257" s="3">
         <v>45762</v>
       </c>
-      <c r="C257" t="s">
-        <v>777</v>
-      </c>
-      <c r="D257" t="s">
-        <v>778</v>
+      <c r="C257" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="D257" s="4" t="s">
+        <v>773</v>
       </c>
       <c r="E257" t="s">
         <v>11</v>
@@ -10677,7 +10705,7 @@
         <v>12</v>
       </c>
       <c r="G257" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="H257">
         <v>0.16669999999999999</v>
@@ -10693,11 +10721,11 @@
       <c r="B258" s="3">
         <v>45762</v>
       </c>
-      <c r="C258" t="s">
-        <v>780</v>
-      </c>
-      <c r="D258" t="s">
-        <v>781</v>
+      <c r="C258" s="4" t="s">
+        <v>775</v>
+      </c>
+      <c r="D258" s="4" t="s">
+        <v>776</v>
       </c>
       <c r="E258" t="s">
         <v>11</v>
@@ -10706,7 +10734,7 @@
         <v>12</v>
       </c>
       <c r="G258" t="s">
-        <v>782</v>
+        <v>777</v>
       </c>
       <c r="H258">
         <v>0.16669999999999999</v>
@@ -10722,11 +10750,11 @@
       <c r="B259" s="3">
         <v>45762</v>
       </c>
-      <c r="C259" t="s">
-        <v>783</v>
-      </c>
-      <c r="D259" t="s">
-        <v>784</v>
+      <c r="C259" s="4" t="s">
+        <v>778</v>
+      </c>
+      <c r="D259" s="4" t="s">
+        <v>779</v>
       </c>
       <c r="E259" t="s">
         <v>11</v>
@@ -10735,7 +10763,7 @@
         <v>16</v>
       </c>
       <c r="G259" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="H259">
         <v>0.16669999999999999</v>
@@ -10751,11 +10779,11 @@
       <c r="B260" s="3">
         <v>45762</v>
       </c>
-      <c r="C260" t="s">
-        <v>786</v>
-      </c>
-      <c r="D260" t="s">
-        <v>787</v>
+      <c r="C260" s="4" t="s">
+        <v>781</v>
+      </c>
+      <c r="D260" s="4" t="s">
+        <v>782</v>
       </c>
       <c r="E260" t="s">
         <v>11</v>
@@ -10764,7 +10792,7 @@
         <v>16</v>
       </c>
       <c r="G260" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="H260">
         <v>0.16669999999999999</v>
@@ -10780,11 +10808,11 @@
       <c r="B261" s="3">
         <v>45762</v>
       </c>
-      <c r="C261" t="s">
-        <v>789</v>
-      </c>
-      <c r="D261" t="s">
-        <v>790</v>
+      <c r="C261" s="4" t="s">
+        <v>784</v>
+      </c>
+      <c r="D261" s="4" t="s">
+        <v>785</v>
       </c>
       <c r="E261" t="s">
         <v>11</v>
@@ -10793,7 +10821,7 @@
         <v>12</v>
       </c>
       <c r="G261" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="H261">
         <v>0.16669999999999999</v>
@@ -10809,11 +10837,11 @@
       <c r="B262" s="3">
         <v>45762</v>
       </c>
-      <c r="C262" t="s">
-        <v>792</v>
-      </c>
-      <c r="D262" t="s">
-        <v>793</v>
+      <c r="C262" s="4" t="s">
+        <v>787</v>
+      </c>
+      <c r="D262" s="4" t="s">
+        <v>788</v>
       </c>
       <c r="E262" t="s">
         <v>11</v>
@@ -10822,7 +10850,7 @@
         <v>16</v>
       </c>
       <c r="G262" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
       <c r="H262">
         <v>0.16669999999999999</v>
@@ -10838,11 +10866,11 @@
       <c r="B263" s="3">
         <v>45762</v>
       </c>
-      <c r="C263" t="s">
-        <v>795</v>
-      </c>
-      <c r="D263" t="s">
-        <v>796</v>
+      <c r="C263" s="4" t="s">
+        <v>790</v>
+      </c>
+      <c r="D263" s="4" t="s">
+        <v>791</v>
       </c>
       <c r="E263" t="s">
         <v>11</v>
@@ -10851,7 +10879,7 @@
         <v>16</v>
       </c>
       <c r="G263" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="H263">
         <v>0.16669999999999999</v>
@@ -10867,11 +10895,11 @@
       <c r="B264" s="3">
         <v>45762</v>
       </c>
-      <c r="C264" t="s">
-        <v>798</v>
-      </c>
-      <c r="D264" t="s">
-        <v>799</v>
+      <c r="C264" s="4" t="s">
+        <v>793</v>
+      </c>
+      <c r="D264" s="4" t="s">
+        <v>794</v>
       </c>
       <c r="E264" t="s">
         <v>11</v>
@@ -10880,7 +10908,7 @@
         <v>16</v>
       </c>
       <c r="G264" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="H264">
         <v>0.16669999999999999</v>
@@ -10896,11 +10924,11 @@
       <c r="B265" s="3">
         <v>45762</v>
       </c>
-      <c r="C265" t="s">
-        <v>801</v>
-      </c>
-      <c r="D265" t="s">
-        <v>802</v>
+      <c r="C265" s="4" t="s">
+        <v>796</v>
+      </c>
+      <c r="D265" s="4" t="s">
+        <v>797</v>
       </c>
       <c r="E265" t="s">
         <v>11</v>
@@ -10909,7 +10937,7 @@
         <v>12</v>
       </c>
       <c r="G265" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="H265">
         <v>0.16669999999999999</v>
@@ -10925,11 +10953,11 @@
       <c r="B266" s="3">
         <v>45762</v>
       </c>
-      <c r="C266" t="s">
-        <v>804</v>
-      </c>
-      <c r="D266" t="s">
-        <v>805</v>
+      <c r="C266" s="4" t="s">
+        <v>799</v>
+      </c>
+      <c r="D266" s="4" t="s">
+        <v>800</v>
       </c>
       <c r="E266" t="s">
         <v>11</v>
@@ -10938,7 +10966,7 @@
         <v>16</v>
       </c>
       <c r="G266" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="H266">
         <v>0.16669999999999999</v>
@@ -10954,11 +10982,11 @@
       <c r="B267" s="3">
         <v>45762</v>
       </c>
-      <c r="C267" t="s">
-        <v>807</v>
-      </c>
-      <c r="D267" t="s">
-        <v>808</v>
+      <c r="C267" s="4" t="s">
+        <v>802</v>
+      </c>
+      <c r="D267" s="4" t="s">
+        <v>803</v>
       </c>
       <c r="E267" t="s">
         <v>11</v>
@@ -10967,7 +10995,7 @@
         <v>12</v>
       </c>
       <c r="G267" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="H267">
         <v>0.16669999999999999</v>
@@ -10983,11 +11011,11 @@
       <c r="B268" s="3">
         <v>45762</v>
       </c>
-      <c r="C268" t="s">
-        <v>810</v>
-      </c>
-      <c r="D268" t="s">
-        <v>811</v>
+      <c r="C268" s="4" t="s">
+        <v>805</v>
+      </c>
+      <c r="D268" s="4" t="s">
+        <v>806</v>
       </c>
       <c r="E268" t="s">
         <v>11</v>
@@ -10996,7 +11024,7 @@
         <v>12</v>
       </c>
       <c r="G268" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="H268">
         <v>0.16669999999999999</v>
@@ -11012,11 +11040,11 @@
       <c r="B269" s="3">
         <v>45762</v>
       </c>
-      <c r="C269" t="s">
-        <v>813</v>
-      </c>
-      <c r="D269" t="s">
-        <v>814</v>
+      <c r="C269" s="4" t="s">
+        <v>808</v>
+      </c>
+      <c r="D269" s="4" t="s">
+        <v>809</v>
       </c>
       <c r="E269" t="s">
         <v>11</v>
@@ -11025,7 +11053,7 @@
         <v>16</v>
       </c>
       <c r="G269" t="s">
-        <v>815</v>
+        <v>810</v>
       </c>
       <c r="H269">
         <v>0.16669999999999999</v>
@@ -11041,11 +11069,11 @@
       <c r="B270" s="3">
         <v>45762</v>
       </c>
-      <c r="C270" t="s">
-        <v>816</v>
-      </c>
-      <c r="D270" t="s">
-        <v>817</v>
+      <c r="C270" s="4" t="s">
+        <v>811</v>
+      </c>
+      <c r="D270" s="4" t="s">
+        <v>812</v>
       </c>
       <c r="E270" t="s">
         <v>11</v>
@@ -11054,7 +11082,7 @@
         <v>16</v>
       </c>
       <c r="G270" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="H270">
         <v>0.16669999999999999</v>
@@ -11070,11 +11098,11 @@
       <c r="B271" s="3">
         <v>45762</v>
       </c>
-      <c r="C271" t="s">
-        <v>819</v>
-      </c>
-      <c r="D271" t="s">
-        <v>820</v>
+      <c r="C271" s="4" t="s">
+        <v>814</v>
+      </c>
+      <c r="D271" s="4" t="s">
+        <v>815</v>
       </c>
       <c r="E271" t="s">
         <v>11</v>
@@ -11083,7 +11111,7 @@
         <v>16</v>
       </c>
       <c r="G271" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
       <c r="H271">
         <v>0.16669999999999999</v>
@@ -11099,11 +11127,11 @@
       <c r="B272" s="3">
         <v>45762</v>
       </c>
-      <c r="C272" t="s">
-        <v>822</v>
-      </c>
-      <c r="D272" t="s">
-        <v>823</v>
+      <c r="C272" s="4" t="s">
+        <v>817</v>
+      </c>
+      <c r="D272" s="4" t="s">
+        <v>818</v>
       </c>
       <c r="E272" t="s">
         <v>11</v>
@@ -11112,7 +11140,7 @@
         <v>16</v>
       </c>
       <c r="G272" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="H272">
         <v>0.16669999999999999</v>
@@ -11128,11 +11156,11 @@
       <c r="B273" s="3">
         <v>45762</v>
       </c>
-      <c r="C273" t="s">
-        <v>825</v>
-      </c>
-      <c r="D273" t="s">
-        <v>826</v>
+      <c r="C273" s="4" t="s">
+        <v>820</v>
+      </c>
+      <c r="D273" s="4" t="s">
+        <v>821</v>
       </c>
       <c r="E273" t="s">
         <v>11</v>
@@ -11141,7 +11169,7 @@
         <v>16</v>
       </c>
       <c r="G273" t="s">
-        <v>827</v>
+        <v>822</v>
       </c>
       <c r="H273">
         <v>0.16669999999999999</v>
@@ -11157,11 +11185,11 @@
       <c r="B274" s="3">
         <v>45762</v>
       </c>
-      <c r="C274" t="s">
-        <v>828</v>
-      </c>
-      <c r="D274" t="s">
-        <v>829</v>
+      <c r="C274" s="4" t="s">
+        <v>823</v>
+      </c>
+      <c r="D274" s="4" t="s">
+        <v>824</v>
       </c>
       <c r="E274" t="s">
         <v>11</v>
@@ -11170,7 +11198,7 @@
         <v>16</v>
       </c>
       <c r="G274" t="s">
-        <v>830</v>
+        <v>825</v>
       </c>
       <c r="H274">
         <v>0.16669999999999999</v>
@@ -11186,11 +11214,11 @@
       <c r="B275" s="3">
         <v>45762</v>
       </c>
-      <c r="C275" t="s">
-        <v>831</v>
-      </c>
-      <c r="D275" t="s">
-        <v>832</v>
+      <c r="C275" s="4" t="s">
+        <v>826</v>
+      </c>
+      <c r="D275" s="4" t="s">
+        <v>827</v>
       </c>
       <c r="E275" t="s">
         <v>11</v>
@@ -11199,7 +11227,7 @@
         <v>12</v>
       </c>
       <c r="G275" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="H275">
         <v>0.16669999999999999</v>
@@ -11215,11 +11243,11 @@
       <c r="B276" s="3">
         <v>45762</v>
       </c>
-      <c r="C276" t="s">
-        <v>834</v>
-      </c>
-      <c r="D276" t="s">
-        <v>835</v>
+      <c r="C276" s="4" t="s">
+        <v>829</v>
+      </c>
+      <c r="D276" s="4" t="s">
+        <v>830</v>
       </c>
       <c r="E276" t="s">
         <v>11</v>
@@ -11228,7 +11256,7 @@
         <v>16</v>
       </c>
       <c r="G276" t="s">
-        <v>836</v>
+        <v>831</v>
       </c>
       <c r="H276">
         <v>0.16669999999999999</v>
@@ -11244,11 +11272,11 @@
       <c r="B277" s="3">
         <v>45762</v>
       </c>
-      <c r="C277" t="s">
-        <v>837</v>
-      </c>
-      <c r="D277" t="s">
-        <v>838</v>
+      <c r="C277" s="4" t="s">
+        <v>832</v>
+      </c>
+      <c r="D277" s="4" t="s">
+        <v>833</v>
       </c>
       <c r="E277" t="s">
         <v>11</v>
@@ -11257,7 +11285,7 @@
         <v>12</v>
       </c>
       <c r="G277" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="H277">
         <v>0.16669999999999999</v>
@@ -11273,11 +11301,11 @@
       <c r="B278" s="3">
         <v>45762</v>
       </c>
-      <c r="C278" t="s">
-        <v>840</v>
-      </c>
-      <c r="D278" t="s">
-        <v>841</v>
+      <c r="C278" s="4" t="s">
+        <v>835</v>
+      </c>
+      <c r="D278" s="4" t="s">
+        <v>836</v>
       </c>
       <c r="E278" t="s">
         <v>11</v>
@@ -11286,7 +11314,7 @@
         <v>16</v>
       </c>
       <c r="G278" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="H278">
         <v>0.16669999999999999</v>
@@ -11302,11 +11330,11 @@
       <c r="B279" s="3">
         <v>45762</v>
       </c>
-      <c r="C279" t="s">
-        <v>843</v>
-      </c>
-      <c r="D279" t="s">
-        <v>844</v>
+      <c r="C279" s="4" t="s">
+        <v>838</v>
+      </c>
+      <c r="D279" s="4" t="s">
+        <v>839</v>
       </c>
       <c r="E279" t="s">
         <v>11</v>
@@ -11315,7 +11343,7 @@
         <v>12</v>
       </c>
       <c r="G279" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="H279">
         <v>0.16669999999999999</v>
@@ -11331,11 +11359,11 @@
       <c r="B280" s="3">
         <v>45762</v>
       </c>
-      <c r="C280" t="s">
-        <v>846</v>
-      </c>
-      <c r="D280" t="s">
-        <v>847</v>
+      <c r="C280" s="4" t="s">
+        <v>841</v>
+      </c>
+      <c r="D280" s="4" t="s">
+        <v>842</v>
       </c>
       <c r="E280" t="s">
         <v>11</v>
@@ -11344,7 +11372,7 @@
         <v>16</v>
       </c>
       <c r="G280" t="s">
-        <v>848</v>
+        <v>843</v>
       </c>
       <c r="H280">
         <v>0.16669999999999999</v>
@@ -11360,11 +11388,11 @@
       <c r="B281" s="3">
         <v>45762</v>
       </c>
-      <c r="C281" t="s">
-        <v>849</v>
-      </c>
-      <c r="D281" t="s">
-        <v>850</v>
+      <c r="C281" s="4" t="s">
+        <v>844</v>
+      </c>
+      <c r="D281" s="4" t="s">
+        <v>845</v>
       </c>
       <c r="E281" t="s">
         <v>11</v>
@@ -11373,7 +11401,7 @@
         <v>16</v>
       </c>
       <c r="G281" t="s">
-        <v>851</v>
+        <v>846</v>
       </c>
       <c r="H281">
         <v>0.16669999999999999</v>
@@ -11389,11 +11417,11 @@
       <c r="B282" s="3">
         <v>45762</v>
       </c>
-      <c r="C282" t="s">
-        <v>852</v>
-      </c>
-      <c r="D282" t="s">
-        <v>853</v>
+      <c r="C282" s="4" t="s">
+        <v>847</v>
+      </c>
+      <c r="D282" s="4" t="s">
+        <v>848</v>
       </c>
       <c r="E282" t="s">
         <v>11</v>
@@ -11402,7 +11430,7 @@
         <v>12</v>
       </c>
       <c r="G282" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="H282">
         <v>0.16669999999999999</v>
@@ -11418,11 +11446,11 @@
       <c r="B283" s="3">
         <v>45762</v>
       </c>
-      <c r="C283" t="s">
-        <v>855</v>
-      </c>
-      <c r="D283" t="s">
-        <v>856</v>
+      <c r="C283" s="4" t="s">
+        <v>850</v>
+      </c>
+      <c r="D283" s="4" t="s">
+        <v>851</v>
       </c>
       <c r="E283" t="s">
         <v>11</v>
@@ -11431,7 +11459,7 @@
         <v>12</v>
       </c>
       <c r="G283" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="H283">
         <v>0.16669999999999999</v>
@@ -11447,11 +11475,11 @@
       <c r="B284" s="3">
         <v>45762</v>
       </c>
-      <c r="C284" t="s">
-        <v>858</v>
-      </c>
-      <c r="D284" t="s">
-        <v>859</v>
+      <c r="C284" s="4" t="s">
+        <v>853</v>
+      </c>
+      <c r="D284" s="4" t="s">
+        <v>854</v>
       </c>
       <c r="E284" t="s">
         <v>11</v>
@@ -11460,7 +11488,7 @@
         <v>16</v>
       </c>
       <c r="G284" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="H284">
         <v>0.16669999999999999</v>
@@ -11476,11 +11504,11 @@
       <c r="B285" s="3">
         <v>45762</v>
       </c>
-      <c r="C285" t="s">
-        <v>861</v>
-      </c>
-      <c r="D285" t="s">
-        <v>862</v>
+      <c r="C285" s="4" t="s">
+        <v>856</v>
+      </c>
+      <c r="D285" s="4" t="s">
+        <v>857</v>
       </c>
       <c r="E285" t="s">
         <v>11</v>
@@ -11489,7 +11517,7 @@
         <v>16</v>
       </c>
       <c r="G285" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="H285">
         <v>0.16669999999999999</v>
@@ -11505,11 +11533,11 @@
       <c r="B286" s="3">
         <v>45762</v>
       </c>
-      <c r="C286" t="s">
-        <v>864</v>
-      </c>
-      <c r="D286" t="s">
-        <v>865</v>
+      <c r="C286" s="4" t="s">
+        <v>859</v>
+      </c>
+      <c r="D286" s="4" t="s">
+        <v>860</v>
       </c>
       <c r="E286" t="s">
         <v>11</v>
@@ -11518,7 +11546,7 @@
         <v>12</v>
       </c>
       <c r="G286" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="H286">
         <v>0.16669999999999999</v>
@@ -11534,11 +11562,11 @@
       <c r="B287" s="3">
         <v>45762</v>
       </c>
-      <c r="C287" t="s">
-        <v>867</v>
-      </c>
-      <c r="D287" t="s">
-        <v>868</v>
+      <c r="C287" s="4" t="s">
+        <v>862</v>
+      </c>
+      <c r="D287" s="4" t="s">
+        <v>863</v>
       </c>
       <c r="E287" t="s">
         <v>11</v>
@@ -11547,7 +11575,7 @@
         <v>16</v>
       </c>
       <c r="G287" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="H287">
         <v>0.16669999999999999</v>
@@ -11563,11 +11591,11 @@
       <c r="B288" s="3">
         <v>45762</v>
       </c>
-      <c r="C288" t="s">
-        <v>870</v>
-      </c>
-      <c r="D288" t="s">
-        <v>871</v>
+      <c r="C288" s="4" t="s">
+        <v>865</v>
+      </c>
+      <c r="D288" s="4" t="s">
+        <v>866</v>
       </c>
       <c r="E288" t="s">
         <v>11</v>
@@ -11576,7 +11604,7 @@
         <v>12</v>
       </c>
       <c r="G288" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="H288">
         <v>0.16669999999999999</v>
@@ -11592,11 +11620,11 @@
       <c r="B289" s="3">
         <v>45762</v>
       </c>
-      <c r="C289" t="s">
-        <v>873</v>
-      </c>
-      <c r="D289" t="s">
-        <v>874</v>
+      <c r="C289" s="4" t="s">
+        <v>868</v>
+      </c>
+      <c r="D289" s="4" t="s">
+        <v>869</v>
       </c>
       <c r="E289" t="s">
         <v>11</v>
@@ -11605,7 +11633,7 @@
         <v>16</v>
       </c>
       <c r="G289" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="H289">
         <v>0.16669999999999999</v>
@@ -11621,11 +11649,11 @@
       <c r="B290" s="3">
         <v>45762</v>
       </c>
-      <c r="C290" t="s">
-        <v>876</v>
-      </c>
-      <c r="D290" t="s">
-        <v>877</v>
+      <c r="C290" s="4" t="s">
+        <v>871</v>
+      </c>
+      <c r="D290" s="4" t="s">
+        <v>872</v>
       </c>
       <c r="E290" t="s">
         <v>11</v>
@@ -11634,7 +11662,7 @@
         <v>16</v>
       </c>
       <c r="G290" t="s">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="H290">
         <v>0.16669999999999999</v>
@@ -11650,11 +11678,11 @@
       <c r="B291" s="3">
         <v>45762</v>
       </c>
-      <c r="C291" t="s">
-        <v>879</v>
-      </c>
-      <c r="D291" t="s">
-        <v>880</v>
+      <c r="C291" s="4" t="s">
+        <v>874</v>
+      </c>
+      <c r="D291" s="4" t="s">
+        <v>875</v>
       </c>
       <c r="E291" t="s">
         <v>11</v>
@@ -11663,7 +11691,7 @@
         <v>16</v>
       </c>
       <c r="G291" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
       <c r="H291">
         <v>0.16669999999999999</v>
@@ -11679,11 +11707,11 @@
       <c r="B292" s="3">
         <v>45762</v>
       </c>
-      <c r="C292" t="s">
-        <v>882</v>
-      </c>
-      <c r="D292" t="s">
-        <v>883</v>
+      <c r="C292" s="4" t="s">
+        <v>877</v>
+      </c>
+      <c r="D292" s="4" t="s">
+        <v>878</v>
       </c>
       <c r="E292" t="s">
         <v>11</v>
@@ -11692,7 +11720,7 @@
         <v>12</v>
       </c>
       <c r="G292" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="H292">
         <v>0.16669999999999999</v>
@@ -11708,11 +11736,11 @@
       <c r="B293" s="3">
         <v>45762</v>
       </c>
-      <c r="C293" t="s">
-        <v>885</v>
-      </c>
-      <c r="D293" t="s">
-        <v>886</v>
+      <c r="C293" s="4" t="s">
+        <v>880</v>
+      </c>
+      <c r="D293" s="4" t="s">
+        <v>881</v>
       </c>
       <c r="E293" t="s">
         <v>11</v>
@@ -11721,7 +11749,7 @@
         <v>12</v>
       </c>
       <c r="G293" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
       <c r="H293">
         <v>0.16669999999999999</v>
@@ -11737,11 +11765,11 @@
       <c r="B294" s="3">
         <v>45762</v>
       </c>
-      <c r="C294" t="s">
-        <v>888</v>
-      </c>
-      <c r="D294" t="s">
-        <v>889</v>
+      <c r="C294" s="4" t="s">
+        <v>883</v>
+      </c>
+      <c r="D294" s="4" t="s">
+        <v>884</v>
       </c>
       <c r="E294" t="s">
         <v>11</v>
@@ -11750,7 +11778,7 @@
         <v>16</v>
       </c>
       <c r="G294" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="H294">
         <v>0.16669999999999999</v>
@@ -11766,11 +11794,11 @@
       <c r="B295" s="3">
         <v>45762</v>
       </c>
-      <c r="C295" t="s">
-        <v>891</v>
-      </c>
-      <c r="D295" t="s">
-        <v>892</v>
+      <c r="C295" s="4" t="s">
+        <v>886</v>
+      </c>
+      <c r="D295" s="4" t="s">
+        <v>887</v>
       </c>
       <c r="E295" t="s">
         <v>11</v>
@@ -11779,7 +11807,7 @@
         <v>16</v>
       </c>
       <c r="G295" t="s">
-        <v>893</v>
+        <v>888</v>
       </c>
       <c r="H295">
         <v>0.16669999999999999</v>
@@ -11795,11 +11823,11 @@
       <c r="B296" s="3">
         <v>45762</v>
       </c>
-      <c r="C296" t="s">
-        <v>894</v>
-      </c>
-      <c r="D296" t="s">
-        <v>895</v>
+      <c r="C296" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="D296" s="4" t="s">
+        <v>890</v>
       </c>
       <c r="E296" t="s">
         <v>11</v>
@@ -11808,7 +11836,7 @@
         <v>16</v>
       </c>
       <c r="G296" t="s">
-        <v>896</v>
+        <v>891</v>
       </c>
       <c r="H296">
         <v>0.16669999999999999</v>
@@ -11824,11 +11852,11 @@
       <c r="B297" s="3">
         <v>45762</v>
       </c>
-      <c r="C297" t="s">
-        <v>897</v>
-      </c>
-      <c r="D297" t="s">
-        <v>898</v>
+      <c r="C297" s="4" t="s">
+        <v>892</v>
+      </c>
+      <c r="D297" s="4" t="s">
+        <v>893</v>
       </c>
       <c r="E297" t="s">
         <v>11</v>
@@ -11837,7 +11865,7 @@
         <v>16</v>
       </c>
       <c r="G297" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="H297">
         <v>0.16669999999999999</v>
@@ -11853,11 +11881,11 @@
       <c r="B298" s="3">
         <v>45762</v>
       </c>
-      <c r="C298" t="s">
-        <v>900</v>
-      </c>
-      <c r="D298" t="s">
-        <v>901</v>
+      <c r="C298" s="4" t="s">
+        <v>895</v>
+      </c>
+      <c r="D298" s="4" t="s">
+        <v>896</v>
       </c>
       <c r="E298" t="s">
         <v>11</v>
@@ -11866,7 +11894,7 @@
         <v>16</v>
       </c>
       <c r="G298" t="s">
-        <v>902</v>
+        <v>897</v>
       </c>
       <c r="H298">
         <v>0.16669999999999999</v>
@@ -11882,11 +11910,11 @@
       <c r="B299" s="3">
         <v>45762</v>
       </c>
-      <c r="C299" t="s">
-        <v>903</v>
-      </c>
-      <c r="D299" t="s">
-        <v>904</v>
+      <c r="C299" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="D299" s="4" t="s">
+        <v>899</v>
       </c>
       <c r="E299" t="s">
         <v>11</v>
@@ -11895,7 +11923,7 @@
         <v>16</v>
       </c>
       <c r="G299" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="H299">
         <v>0.16669999999999999</v>
@@ -11911,11 +11939,11 @@
       <c r="B300" s="3">
         <v>45762</v>
       </c>
-      <c r="C300" t="s">
-        <v>906</v>
-      </c>
-      <c r="D300" t="s">
-        <v>907</v>
+      <c r="C300" s="4" t="s">
+        <v>901</v>
+      </c>
+      <c r="D300" s="4" t="s">
+        <v>902</v>
       </c>
       <c r="E300" t="s">
         <v>11</v>
@@ -11924,7 +11952,7 @@
         <v>16</v>
       </c>
       <c r="G300" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="H300">
         <v>0.16669999999999999</v>
@@ -11940,11 +11968,11 @@
       <c r="B301" s="3">
         <v>45762</v>
       </c>
-      <c r="C301" t="s">
-        <v>909</v>
-      </c>
-      <c r="D301" t="s">
-        <v>910</v>
+      <c r="C301" s="4" t="s">
+        <v>904</v>
+      </c>
+      <c r="D301" s="4" t="s">
+        <v>905</v>
       </c>
       <c r="E301" t="s">
         <v>11</v>
@@ -11953,7 +11981,7 @@
         <v>16</v>
       </c>
       <c r="G301" t="s">
-        <v>911</v>
+        <v>906</v>
       </c>
       <c r="H301">
         <v>0.16669999999999999</v>
@@ -11969,11 +11997,11 @@
       <c r="B302" s="3">
         <v>45762</v>
       </c>
-      <c r="C302" t="s">
-        <v>912</v>
-      </c>
-      <c r="D302" t="s">
-        <v>913</v>
+      <c r="C302" s="4" t="s">
+        <v>907</v>
+      </c>
+      <c r="D302" s="4" t="s">
+        <v>908</v>
       </c>
       <c r="E302" t="s">
         <v>11</v>
@@ -11982,7 +12010,7 @@
         <v>16</v>
       </c>
       <c r="G302" t="s">
-        <v>914</v>
+        <v>909</v>
       </c>
       <c r="H302">
         <v>0.16669999999999999</v>
@@ -11998,11 +12026,11 @@
       <c r="B303" s="3">
         <v>45762</v>
       </c>
-      <c r="C303" t="s">
-        <v>915</v>
-      </c>
-      <c r="D303" t="s">
-        <v>916</v>
+      <c r="C303" s="4" t="s">
+        <v>910</v>
+      </c>
+      <c r="D303" s="4" t="s">
+        <v>911</v>
       </c>
       <c r="E303" t="s">
         <v>11</v>
@@ -12011,7 +12039,7 @@
         <v>16</v>
       </c>
       <c r="G303" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="H303">
         <v>0.16669999999999999</v>
@@ -12027,11 +12055,11 @@
       <c r="B304" s="3">
         <v>45762</v>
       </c>
-      <c r="C304" t="s">
-        <v>918</v>
-      </c>
-      <c r="D304" t="s">
-        <v>919</v>
+      <c r="C304" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="D304" s="4" t="s">
+        <v>914</v>
       </c>
       <c r="E304" t="s">
         <v>11</v>
@@ -12040,7 +12068,7 @@
         <v>12</v>
       </c>
       <c r="G304" t="s">
-        <v>920</v>
+        <v>915</v>
       </c>
       <c r="H304">
         <v>0.16669999999999999</v>
@@ -12056,11 +12084,11 @@
       <c r="B305" s="3">
         <v>45762</v>
       </c>
-      <c r="C305" t="s">
-        <v>921</v>
-      </c>
-      <c r="D305" t="s">
-        <v>922</v>
+      <c r="C305" s="4" t="s">
+        <v>916</v>
+      </c>
+      <c r="D305" s="4" t="s">
+        <v>917</v>
       </c>
       <c r="E305" t="s">
         <v>11</v>
@@ -12069,7 +12097,7 @@
         <v>16</v>
       </c>
       <c r="G305" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="H305">
         <v>0.16669999999999999</v>
@@ -12085,11 +12113,11 @@
       <c r="B306" s="3">
         <v>45762</v>
       </c>
-      <c r="C306" t="s">
-        <v>924</v>
-      </c>
-      <c r="D306" t="s">
-        <v>925</v>
+      <c r="C306" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="D306" s="4" t="s">
+        <v>920</v>
       </c>
       <c r="E306" t="s">
         <v>11</v>
@@ -12098,7 +12126,7 @@
         <v>16</v>
       </c>
       <c r="G306" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="H306">
         <v>0.16669999999999999</v>
@@ -12114,11 +12142,11 @@
       <c r="B307" s="3">
         <v>45762</v>
       </c>
-      <c r="C307" t="s">
-        <v>927</v>
-      </c>
-      <c r="D307" t="s">
-        <v>928</v>
+      <c r="C307" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="D307" s="4" t="s">
+        <v>923</v>
       </c>
       <c r="E307" t="s">
         <v>11</v>
@@ -12127,7 +12155,7 @@
         <v>16</v>
       </c>
       <c r="G307" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
       <c r="H307">
         <v>0.16669999999999999</v>
@@ -12143,11 +12171,11 @@
       <c r="B308" s="3">
         <v>45762</v>
       </c>
-      <c r="C308" t="s">
-        <v>930</v>
-      </c>
-      <c r="D308" t="s">
-        <v>931</v>
+      <c r="C308" s="4" t="s">
+        <v>925</v>
+      </c>
+      <c r="D308" s="4" t="s">
+        <v>926</v>
       </c>
       <c r="E308" t="s">
         <v>11</v>
@@ -12156,7 +12184,7 @@
         <v>12</v>
       </c>
       <c r="G308" t="s">
-        <v>932</v>
+        <v>927</v>
       </c>
       <c r="H308">
         <v>0.16669999999999999</v>
@@ -12172,11 +12200,11 @@
       <c r="B309" s="3">
         <v>45762</v>
       </c>
-      <c r="C309" t="s">
-        <v>933</v>
-      </c>
-      <c r="D309" t="s">
-        <v>934</v>
+      <c r="C309" s="4" t="s">
+        <v>928</v>
+      </c>
+      <c r="D309" s="4" t="s">
+        <v>929</v>
       </c>
       <c r="E309" t="s">
         <v>11</v>
@@ -12185,7 +12213,7 @@
         <v>16</v>
       </c>
       <c r="G309" t="s">
-        <v>935</v>
+        <v>930</v>
       </c>
       <c r="H309">
         <v>0.16669999999999999</v>
@@ -12201,11 +12229,11 @@
       <c r="B310" s="3">
         <v>45762</v>
       </c>
-      <c r="C310" t="s">
-        <v>936</v>
-      </c>
-      <c r="D310" t="s">
-        <v>937</v>
+      <c r="C310" s="4" t="s">
+        <v>931</v>
+      </c>
+      <c r="D310" s="4" t="s">
+        <v>932</v>
       </c>
       <c r="E310" t="s">
         <v>11</v>
@@ -12214,7 +12242,7 @@
         <v>12</v>
       </c>
       <c r="G310" t="s">
-        <v>938</v>
+        <v>933</v>
       </c>
       <c r="H310">
         <v>0.16669999999999999</v>
@@ -12230,11 +12258,11 @@
       <c r="B311" s="3">
         <v>45762</v>
       </c>
-      <c r="C311" t="s">
-        <v>939</v>
-      </c>
-      <c r="D311" t="s">
-        <v>940</v>
+      <c r="C311" s="4" t="s">
+        <v>934</v>
+      </c>
+      <c r="D311" s="4" t="s">
+        <v>935</v>
       </c>
       <c r="E311" t="s">
         <v>11</v>
@@ -12243,7 +12271,7 @@
         <v>16</v>
       </c>
       <c r="G311" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
       <c r="H311">
         <v>0.16669999999999999</v>
@@ -12259,11 +12287,11 @@
       <c r="B312" s="3">
         <v>45762</v>
       </c>
-      <c r="C312" t="s">
-        <v>942</v>
-      </c>
-      <c r="D312" t="s">
-        <v>943</v>
+      <c r="C312" s="4" t="s">
+        <v>937</v>
+      </c>
+      <c r="D312" s="4" t="s">
+        <v>938</v>
       </c>
       <c r="E312" t="s">
         <v>11</v>
@@ -12272,7 +12300,7 @@
         <v>12</v>
       </c>
       <c r="G312" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
       <c r="H312">
         <v>0.16669999999999999</v>
@@ -12288,11 +12316,11 @@
       <c r="B313" s="3">
         <v>45762</v>
       </c>
-      <c r="C313" t="s">
-        <v>945</v>
-      </c>
-      <c r="D313" t="s">
-        <v>946</v>
+      <c r="C313" s="4" t="s">
+        <v>940</v>
+      </c>
+      <c r="D313" s="4" t="s">
+        <v>941</v>
       </c>
       <c r="E313" t="s">
         <v>11</v>
@@ -12301,7 +12329,7 @@
         <v>16</v>
       </c>
       <c r="G313" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="H313">
         <v>0.16669999999999999</v>
